--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3617,6 +3617,132 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125512020</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>577196</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6711856</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Margareta Kling</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Margareta Kling</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3743,6 +3743,6398 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125687087</v>
+      </c>
+      <c r="B28" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>53</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>577157</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6711975</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125687146</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>577165</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6711956</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125687119</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>577190</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6711913</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125687131</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>577148</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6711976</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125687139</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>577090</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6711973</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125687081</v>
+      </c>
+      <c r="B33" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>53</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>577109</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6711890</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125687124</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>577103</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6711980</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125687090</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91131</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>577215</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6711829</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125687134</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>577126</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6711880</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125687136</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>577187</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6711916</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125687079</v>
+      </c>
+      <c r="B38" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>53</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>577171</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6711847</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125687118</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>577129</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6711973</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125687084</v>
+      </c>
+      <c r="B40" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>53</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>577088</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6711963</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125687148</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98186</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>577163</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6711969</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125687088</v>
+      </c>
+      <c r="B42" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>53</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>577173</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6711943</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125687128</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>577194</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6711897</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>125687121</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>577178</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6711912</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125687122</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>577145</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6711917</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125687110</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>577101</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6711989</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125687120</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>577187</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6711920</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125687085</v>
+      </c>
+      <c r="B48" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>53</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>577130</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6711985</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125687125</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>577172</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6711942</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125687086</v>
+      </c>
+      <c r="B50" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>53</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>577150</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6711955</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>125687095</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91166</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>577135</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6711824</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125687144</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>577150</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6711962</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125687150</v>
+      </c>
+      <c r="B53" t="n">
+        <v>5176</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>577174</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6711873</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125687135</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>577117</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6712004</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>125687116</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>577202</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6711890</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>125687133</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>577171</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6711869</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125687111</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>577182</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6711920</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125687145</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>577155</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6711978</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125687142</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>577150</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6711955</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>125687143</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>577152</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6711960</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>125687140</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>577141</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6711960</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>125687097</v>
+      </c>
+      <c r="B62" t="n">
+        <v>4772</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>577154</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6711917</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>125687091</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91166</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>577156</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6711864</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>125687115</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>577167</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6711948</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>125687112</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>577130</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6711953</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>125687132</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>577153</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6711978</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>125687149</v>
+      </c>
+      <c r="B67" t="n">
+        <v>95122</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>2383</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Bågpraktmossa</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Plagiomnium medium</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>577165</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6711852</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>125687152</v>
+      </c>
+      <c r="B68" t="n">
+        <v>102498</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>577131</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6711836</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>12 cm dbh</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>125687127</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>577095</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6711970</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>125687078</v>
+      </c>
+      <c r="B70" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>53</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>577169</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6711894</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>125687093</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91166</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>577243</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6711783</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>125687117</v>
+      </c>
+      <c r="B72" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>577124</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6711978</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>125687129</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>577096</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6711969</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>125687114</v>
+      </c>
+      <c r="B74" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>577145</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6711974</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>125687126</v>
+      </c>
+      <c r="B75" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>577173</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6711932</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>125687082</v>
+      </c>
+      <c r="B76" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>53</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>577110</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6711911</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>125687096</v>
+      </c>
+      <c r="B77" t="n">
+        <v>103700</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>577145</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6711831</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>125687123</v>
+      </c>
+      <c r="B78" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>577090</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6711978</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>125687137</v>
+      </c>
+      <c r="B79" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>577195</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6711896</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>125687092</v>
+      </c>
+      <c r="B80" t="n">
+        <v>91166</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>577169</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6711859</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>125687130</v>
+      </c>
+      <c r="B81" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>577105</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6711976</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>125687083</v>
+      </c>
+      <c r="B82" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>53</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>577154</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6711905</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>125687141</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>577143</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6711958</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>125687151</v>
+      </c>
+      <c r="B84" t="n">
+        <v>5176</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>577176</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6711840</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>125687113</v>
+      </c>
+      <c r="B85" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>577142</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6711971</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>125687094</v>
+      </c>
+      <c r="B86" t="n">
+        <v>91166</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>577189</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6711814</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -3622,12 +3622,7 @@
         <v>125512020</v>
       </c>
       <c r="B27" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3745,15 +3740,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125687087</v>
+        <v>125687083</v>
       </c>
       <c r="B28" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3785,10 +3775,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577157</v>
+        <v>577154</v>
       </c>
       <c r="R28" t="n">
-        <v>6711975</v>
+        <v>6711905</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3847,59 +3837,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125687146</v>
+        <v>125687078</v>
       </c>
       <c r="B29" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577165</v>
+        <v>577169</v>
       </c>
       <c r="R29" t="n">
-        <v>6711956</v>
+        <v>6711894</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3958,15 +3934,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125687119</v>
+        <v>125687111</v>
       </c>
       <c r="B30" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3993,7 +3964,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4007,10 +3978,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577190</v>
+        <v>577182</v>
       </c>
       <c r="R30" t="n">
-        <v>6711913</v>
+        <v>6711920</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4069,59 +4040,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125687131</v>
+        <v>125687079</v>
       </c>
       <c r="B31" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577148</v>
+        <v>577171</v>
       </c>
       <c r="R31" t="n">
-        <v>6711976</v>
+        <v>6711847</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4180,15 +4137,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125687139</v>
+        <v>125687142</v>
       </c>
       <c r="B32" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4229,10 +4181,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577090</v>
+        <v>577150</v>
       </c>
       <c r="R32" t="n">
-        <v>6711973</v>
+        <v>6711955</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4291,50 +4243,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125687081</v>
+        <v>125687123</v>
       </c>
       <c r="B33" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577109</v>
+        <v>577090</v>
       </c>
       <c r="R33" t="n">
-        <v>6711890</v>
+        <v>6711978</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4393,15 +4349,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125687124</v>
+        <v>125687116</v>
       </c>
       <c r="B34" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4428,7 +4379,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4442,10 +4393,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577103</v>
+        <v>577202</v>
       </c>
       <c r="R34" t="n">
-        <v>6711980</v>
+        <v>6711890</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4504,37 +4455,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125687090</v>
+        <v>125687086</v>
       </c>
       <c r="B35" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4544,10 +4490,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577215</v>
+        <v>577150</v>
       </c>
       <c r="R35" t="n">
-        <v>6711829</v>
+        <v>6711955</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4606,15 +4552,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125687134</v>
+        <v>125687121</v>
       </c>
       <c r="B36" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4641,7 +4582,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4655,10 +4596,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577126</v>
+        <v>577178</v>
       </c>
       <c r="R36" t="n">
-        <v>6711880</v>
+        <v>6711912</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4717,15 +4658,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125687136</v>
+        <v>125687127</v>
       </c>
       <c r="B37" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4752,7 +4688,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4760,16 +4696,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577187</v>
+        <v>577095</v>
       </c>
       <c r="R37" t="n">
-        <v>6711916</v>
+        <v>6711970</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4810,6 +4753,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4828,50 +4772,54 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125687079</v>
+        <v>125687122</v>
       </c>
       <c r="B38" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577171</v>
+        <v>577145</v>
       </c>
       <c r="R38" t="n">
-        <v>6711847</v>
+        <v>6711917</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4930,15 +4878,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125687118</v>
+        <v>125687130</v>
       </c>
       <c r="B39" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4965,7 +4908,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4979,10 +4922,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577129</v>
+        <v>577105</v>
       </c>
       <c r="R39" t="n">
-        <v>6711973</v>
+        <v>6711976</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5041,50 +4984,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125687084</v>
+        <v>125687140</v>
       </c>
       <c r="B40" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577088</v>
+        <v>577141</v>
       </c>
       <c r="R40" t="n">
-        <v>6711963</v>
+        <v>6711960</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5143,37 +5090,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125687148</v>
+        <v>125687092</v>
       </c>
       <c r="B41" t="n">
-        <v>98186</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5183,10 +5125,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577163</v>
+        <v>577169</v>
       </c>
       <c r="R41" t="n">
-        <v>6711969</v>
+        <v>6711859</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5245,50 +5187,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125687088</v>
+        <v>125687150</v>
       </c>
       <c r="B42" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5176</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577173</v>
+        <v>577174</v>
       </c>
       <c r="R42" t="n">
-        <v>6711943</v>
+        <v>6711873</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5347,15 +5289,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125687128</v>
+        <v>125687145</v>
       </c>
       <c r="B43" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5382,7 +5319,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5396,10 +5333,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577194</v>
+        <v>577155</v>
       </c>
       <c r="R43" t="n">
-        <v>6711897</v>
+        <v>6711978</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5458,59 +5395,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125687121</v>
+        <v>125687093</v>
       </c>
       <c r="B44" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577178</v>
+        <v>577243</v>
       </c>
       <c r="R44" t="n">
-        <v>6711912</v>
+        <v>6711783</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5569,59 +5492,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125687122</v>
+        <v>125687091</v>
       </c>
       <c r="B45" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577145</v>
+        <v>577156</v>
       </c>
       <c r="R45" t="n">
-        <v>6711917</v>
+        <v>6711864</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5680,66 +5589,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125687110</v>
+        <v>125687090</v>
       </c>
       <c r="B46" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577101</v>
+        <v>577215</v>
       </c>
       <c r="R46" t="n">
-        <v>6711989</v>
+        <v>6711829</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5780,7 +5668,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5799,66 +5686,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125687120</v>
+        <v>125687151</v>
       </c>
       <c r="B47" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5176</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577187</v>
+        <v>577176</v>
       </c>
       <c r="R47" t="n">
-        <v>6711920</v>
+        <v>6711840</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5899,7 +5770,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5918,15 +5788,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125687085</v>
+        <v>125687081</v>
       </c>
       <c r="B48" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5958,10 +5823,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577130</v>
+        <v>577109</v>
       </c>
       <c r="R48" t="n">
-        <v>6711985</v>
+        <v>6711890</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6020,15 +5885,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125687125</v>
+        <v>125687133</v>
       </c>
       <c r="B49" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6055,7 +5915,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6069,10 +5929,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577172</v>
+        <v>577171</v>
       </c>
       <c r="R49" t="n">
-        <v>6711942</v>
+        <v>6711869</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6105,6 +5965,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6131,15 +5996,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125687086</v>
+        <v>125687082</v>
       </c>
       <c r="B50" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6171,10 +6031,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577150</v>
+        <v>577110</v>
       </c>
       <c r="R50" t="n">
-        <v>6711955</v>
+        <v>6711911</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6233,37 +6093,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125687095</v>
+        <v>125687152</v>
       </c>
       <c r="B51" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102553</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>223246</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6273,10 +6128,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577135</v>
+        <v>577131</v>
       </c>
       <c r="R51" t="n">
-        <v>6711824</v>
+        <v>6711836</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6311,12 +6166,18 @@
           <t>2025-06-04</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>12 cm dbh</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6335,15 +6196,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125687144</v>
+        <v>125687131</v>
       </c>
       <c r="B52" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6370,7 +6226,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6384,10 +6240,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577150</v>
+        <v>577148</v>
       </c>
       <c r="R52" t="n">
-        <v>6711962</v>
+        <v>6711976</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6446,15 +6302,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125687150</v>
+        <v>125687149</v>
       </c>
       <c r="B53" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95176</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6462,39 +6313,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>2383</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>577174</v>
+        <v>577165</v>
       </c>
       <c r="R53" t="n">
-        <v>6711873</v>
+        <v>6711852</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6553,15 +6399,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125687135</v>
+        <v>125687136</v>
       </c>
       <c r="B54" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6602,10 +6443,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577117</v>
+        <v>577187</v>
       </c>
       <c r="R54" t="n">
-        <v>6712004</v>
+        <v>6711916</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6664,15 +6505,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125687116</v>
+        <v>125687139</v>
       </c>
       <c r="B55" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6699,7 +6535,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6713,10 +6549,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>577202</v>
+        <v>577090</v>
       </c>
       <c r="R55" t="n">
-        <v>6711890</v>
+        <v>6711973</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6775,59 +6611,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125687133</v>
+        <v>125687084</v>
       </c>
       <c r="B56" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>577171</v>
+        <v>577088</v>
       </c>
       <c r="R56" t="n">
-        <v>6711869</v>
+        <v>6711963</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6860,11 +6682,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6891,59 +6708,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125687111</v>
+        <v>125687095</v>
       </c>
       <c r="B57" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>577182</v>
+        <v>577135</v>
       </c>
       <c r="R57" t="n">
-        <v>6711920</v>
+        <v>6711824</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7002,15 +6805,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125687145</v>
+        <v>125687143</v>
       </c>
       <c r="B58" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7051,10 +6849,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>577155</v>
+        <v>577152</v>
       </c>
       <c r="R58" t="n">
-        <v>6711978</v>
+        <v>6711960</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7113,59 +6911,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125687142</v>
+        <v>125687085</v>
       </c>
       <c r="B59" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>577150</v>
+        <v>577130</v>
       </c>
       <c r="R59" t="n">
-        <v>6711955</v>
+        <v>6711985</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7224,15 +7008,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125687143</v>
+        <v>125687114</v>
       </c>
       <c r="B60" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7259,7 +7038,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7273,10 +7052,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577152</v>
+        <v>577145</v>
       </c>
       <c r="R60" t="n">
-        <v>6711960</v>
+        <v>6711974</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7335,15 +7114,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125687140</v>
+        <v>125687141</v>
       </c>
       <c r="B61" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7384,10 +7158,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>577141</v>
+        <v>577143</v>
       </c>
       <c r="R61" t="n">
-        <v>6711960</v>
+        <v>6711958</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7446,43 +7220,42 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125687097</v>
+        <v>125687144</v>
       </c>
       <c r="B62" t="n">
-        <v>4772</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7491,10 +7264,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577154</v>
+        <v>577150</v>
       </c>
       <c r="R62" t="n">
-        <v>6711917</v>
+        <v>6711962</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7553,50 +7326,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125687091</v>
+        <v>125687128</v>
       </c>
       <c r="B63" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577156</v>
+        <v>577194</v>
       </c>
       <c r="R63" t="n">
-        <v>6711864</v>
+        <v>6711897</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7655,15 +7432,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125687115</v>
+        <v>125687110</v>
       </c>
       <c r="B64" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7690,7 +7462,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7698,16 +7470,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>577167</v>
+        <v>577101</v>
       </c>
       <c r="R64" t="n">
-        <v>6711948</v>
+        <v>6711989</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7748,6 +7527,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7766,15 +7546,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125687112</v>
+        <v>125687113</v>
       </c>
       <c r="B65" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7815,10 +7590,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>577130</v>
+        <v>577142</v>
       </c>
       <c r="R65" t="n">
-        <v>6711953</v>
+        <v>6711971</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7877,15 +7652,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125687132</v>
+        <v>125687112</v>
       </c>
       <c r="B66" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7912,7 +7682,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7926,10 +7696,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>577153</v>
+        <v>577130</v>
       </c>
       <c r="R66" t="n">
-        <v>6711978</v>
+        <v>6711953</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7988,50 +7758,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125687149</v>
+        <v>125687134</v>
       </c>
       <c r="B67" t="n">
-        <v>95122</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2383</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>577165</v>
+        <v>577126</v>
       </c>
       <c r="R67" t="n">
-        <v>6711852</v>
+        <v>6711880</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8090,50 +7864,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125687152</v>
+        <v>125687124</v>
       </c>
       <c r="B68" t="n">
-        <v>102498</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>223246</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>577131</v>
+        <v>577103</v>
       </c>
       <c r="R68" t="n">
-        <v>6711836</v>
+        <v>6711980</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8168,18 +7946,12 @@
           <t>2025-06-04</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>12 cm dbh</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8198,15 +7970,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125687127</v>
+        <v>125687137</v>
       </c>
       <c r="B69" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8233,7 +8000,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8241,23 +8008,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>577095</v>
+        <v>577195</v>
       </c>
       <c r="R69" t="n">
-        <v>6711970</v>
+        <v>6711896</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8298,7 +8058,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8317,50 +8076,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125687078</v>
+        <v>125687126</v>
       </c>
       <c r="B70" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>577169</v>
+        <v>577173</v>
       </c>
       <c r="R70" t="n">
-        <v>6711894</v>
+        <v>6711932</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8419,50 +8182,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125687093</v>
+        <v>125687129</v>
       </c>
       <c r="B71" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>577243</v>
+        <v>577096</v>
       </c>
       <c r="R71" t="n">
-        <v>6711783</v>
+        <v>6711969</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8521,15 +8288,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125687117</v>
+        <v>125687119</v>
       </c>
       <c r="B72" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8570,10 +8332,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>577124</v>
+        <v>577190</v>
       </c>
       <c r="R72" t="n">
-        <v>6711978</v>
+        <v>6711913</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8632,15 +8394,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125687129</v>
+        <v>125687115</v>
       </c>
       <c r="B73" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8667,7 +8424,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8681,10 +8438,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>577096</v>
+        <v>577167</v>
       </c>
       <c r="R73" t="n">
-        <v>6711969</v>
+        <v>6711948</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8743,15 +8500,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125687114</v>
+        <v>125687120</v>
       </c>
       <c r="B74" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8778,7 +8530,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8786,16 +8538,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>577145</v>
+        <v>577187</v>
       </c>
       <c r="R74" t="n">
-        <v>6711974</v>
+        <v>6711920</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8836,6 +8595,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8854,59 +8614,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125687126</v>
+        <v>125687148</v>
       </c>
       <c r="B75" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98241</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>577173</v>
+        <v>577163</v>
       </c>
       <c r="R75" t="n">
-        <v>6711932</v>
+        <v>6711969</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8965,50 +8711,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125687082</v>
+        <v>125687125</v>
       </c>
       <c r="B76" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>577110</v>
+        <v>577172</v>
       </c>
       <c r="R76" t="n">
-        <v>6711911</v>
+        <v>6711942</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9070,12 +8820,7 @@
         <v>125687096</v>
       </c>
       <c r="B77" t="n">
-        <v>103700</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103755</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9169,59 +8914,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125687123</v>
+        <v>125687087</v>
       </c>
       <c r="B78" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>577090</v>
+        <v>577157</v>
       </c>
       <c r="R78" t="n">
-        <v>6711978</v>
+        <v>6711975</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9280,47 +9011,38 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125687137</v>
+        <v>125687097</v>
       </c>
       <c r="B79" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4772</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9329,10 +9051,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>577195</v>
+        <v>577154</v>
       </c>
       <c r="R79" t="n">
-        <v>6711896</v>
+        <v>6711917</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9391,50 +9113,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125687092</v>
+        <v>125687146</v>
       </c>
       <c r="B80" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>577169</v>
+        <v>577165</v>
       </c>
       <c r="R80" t="n">
-        <v>6711859</v>
+        <v>6711956</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9493,59 +9219,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125687130</v>
+        <v>125687088</v>
       </c>
       <c r="B81" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>577105</v>
+        <v>577173</v>
       </c>
       <c r="R81" t="n">
-        <v>6711976</v>
+        <v>6711943</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9604,15 +9316,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125687083</v>
+        <v>125687094</v>
       </c>
       <c r="B82" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9620,21 +9327,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9644,10 +9351,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>577154</v>
+        <v>577189</v>
       </c>
       <c r="R82" t="n">
-        <v>6711905</v>
+        <v>6711814</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9706,15 +9413,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125687141</v>
+        <v>125687132</v>
       </c>
       <c r="B83" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9741,7 +9443,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9755,10 +9457,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>577143</v>
+        <v>577153</v>
       </c>
       <c r="R83" t="n">
-        <v>6711958</v>
+        <v>6711978</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9817,43 +9519,42 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125687151</v>
+        <v>125687117</v>
       </c>
       <c r="B84" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9862,10 +9563,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>577176</v>
+        <v>577124</v>
       </c>
       <c r="R84" t="n">
-        <v>6711840</v>
+        <v>6711978</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9924,15 +9625,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125687113</v>
+        <v>125687118</v>
       </c>
       <c r="B85" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9959,7 +9655,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -9973,10 +9669,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>577142</v>
+        <v>577129</v>
       </c>
       <c r="R85" t="n">
-        <v>6711971</v>
+        <v>6711973</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10035,50 +9731,54 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125687094</v>
+        <v>125687135</v>
       </c>
       <c r="B86" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>577189</v>
+        <v>577117</v>
       </c>
       <c r="R86" t="n">
-        <v>6711814</v>
+        <v>6712004</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -5090,45 +5090,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125687092</v>
+        <v>125687150</v>
       </c>
       <c r="B41" t="n">
-        <v>91220</v>
+        <v>5176</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577169</v>
+        <v>577174</v>
       </c>
       <c r="R41" t="n">
-        <v>6711859</v>
+        <v>6711873</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5187,50 +5192,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125687150</v>
+        <v>125687092</v>
       </c>
       <c r="B42" t="n">
-        <v>5176</v>
+        <v>91220</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577174</v>
+        <v>577169</v>
       </c>
       <c r="R42" t="n">
-        <v>6711873</v>
+        <v>6711859</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5289,54 +5289,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125687145</v>
+        <v>125687093</v>
       </c>
       <c r="B43" t="n">
-        <v>98324</v>
+        <v>91220</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577155</v>
+        <v>577243</v>
       </c>
       <c r="R43" t="n">
-        <v>6711978</v>
+        <v>6711783</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5395,45 +5386,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125687093</v>
+        <v>125687145</v>
       </c>
       <c r="B44" t="n">
-        <v>91220</v>
+        <v>98324</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577243</v>
+        <v>577155</v>
       </c>
       <c r="R44" t="n">
-        <v>6711783</v>
+        <v>6711978</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5996,45 +5996,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125687082</v>
+        <v>125687131</v>
       </c>
       <c r="B50" t="n">
-        <v>96577</v>
+        <v>98324</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577110</v>
+        <v>577148</v>
       </c>
       <c r="R50" t="n">
-        <v>6711911</v>
+        <v>6711976</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6196,54 +6205,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125687131</v>
+        <v>125687082</v>
       </c>
       <c r="B52" t="n">
-        <v>98324</v>
+        <v>96577</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577148</v>
+        <v>577110</v>
       </c>
       <c r="R52" t="n">
-        <v>6711976</v>
+        <v>6711911</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6399,54 +6399,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125687136</v>
+        <v>125687084</v>
       </c>
       <c r="B54" t="n">
-        <v>98324</v>
+        <v>96577</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577187</v>
+        <v>577088</v>
       </c>
       <c r="R54" t="n">
-        <v>6711916</v>
+        <v>6711963</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6505,7 +6496,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125687139</v>
+        <v>125687136</v>
       </c>
       <c r="B55" t="n">
         <v>98324</v>
@@ -6535,7 +6526,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6549,10 +6540,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>577090</v>
+        <v>577187</v>
       </c>
       <c r="R55" t="n">
-        <v>6711973</v>
+        <v>6711916</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6611,45 +6602,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125687084</v>
+        <v>125687139</v>
       </c>
       <c r="B56" t="n">
-        <v>96577</v>
+        <v>98324</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>577088</v>
+        <v>577090</v>
       </c>
       <c r="R56" t="n">
-        <v>6711963</v>
+        <v>6711973</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -9011,38 +9011,42 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125687097</v>
+        <v>125687146</v>
       </c>
       <c r="B79" t="n">
-        <v>4772</v>
+        <v>98324</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9051,10 +9055,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>577154</v>
+        <v>577165</v>
       </c>
       <c r="R79" t="n">
-        <v>6711917</v>
+        <v>6711956</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9113,54 +9117,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125687146</v>
+        <v>125687088</v>
       </c>
       <c r="B80" t="n">
-        <v>98324</v>
+        <v>96577</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>577165</v>
+        <v>577173</v>
       </c>
       <c r="R80" t="n">
-        <v>6711956</v>
+        <v>6711943</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9219,45 +9214,50 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125687088</v>
+        <v>125687097</v>
       </c>
       <c r="B81" t="n">
-        <v>96577</v>
+        <v>4772</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>577173</v>
+        <v>577154</v>
       </c>
       <c r="R81" t="n">
-        <v>6711943</v>
+        <v>6711917</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -3622,7 +3622,7 @@
         <v>125512020</v>
       </c>
       <c r="B27" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>125687083</v>
       </c>
       <c r="B28" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>125687078</v>
       </c>
       <c r="B29" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>125687111</v>
       </c>
       <c r="B30" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>125687079</v>
       </c>
       <c r="B31" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>125687142</v>
       </c>
       <c r="B32" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>125687123</v>
       </c>
       <c r="B33" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>125687116</v>
       </c>
       <c r="B34" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>125687086</v>
       </c>
       <c r="B35" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>125687121</v>
       </c>
       <c r="B36" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>125687127</v>
       </c>
       <c r="B37" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4772,54 +4772,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125687122</v>
+        <v>125687092</v>
       </c>
       <c r="B38" t="n">
-        <v>98324</v>
+        <v>91227</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577145</v>
+        <v>577169</v>
       </c>
       <c r="R38" t="n">
-        <v>6711917</v>
+        <v>6711859</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4878,42 +4869,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125687130</v>
+        <v>125687150</v>
       </c>
       <c r="B39" t="n">
-        <v>98324</v>
+        <v>5176</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4922,10 +4909,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577105</v>
+        <v>577174</v>
       </c>
       <c r="R39" t="n">
-        <v>6711976</v>
+        <v>6711873</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4984,10 +4971,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125687140</v>
+        <v>125687122</v>
       </c>
       <c r="B40" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5014,7 +5001,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5028,10 +5015,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577141</v>
+        <v>577145</v>
       </c>
       <c r="R40" t="n">
-        <v>6711960</v>
+        <v>6711917</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5090,38 +5077,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125687150</v>
+        <v>125687130</v>
       </c>
       <c r="B41" t="n">
-        <v>5176</v>
+        <v>98331</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5130,10 +5121,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577174</v>
+        <v>577105</v>
       </c>
       <c r="R41" t="n">
-        <v>6711873</v>
+        <v>6711976</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5192,45 +5183,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125687092</v>
+        <v>125687140</v>
       </c>
       <c r="B42" t="n">
-        <v>91220</v>
+        <v>98331</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577169</v>
+        <v>577141</v>
       </c>
       <c r="R42" t="n">
-        <v>6711859</v>
+        <v>6711960</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5292,7 +5292,7 @@
         <v>125687093</v>
       </c>
       <c r="B43" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5386,54 +5386,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125687145</v>
+        <v>125687091</v>
       </c>
       <c r="B44" t="n">
-        <v>98324</v>
+        <v>91227</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577155</v>
+        <v>577156</v>
       </c>
       <c r="R44" t="n">
-        <v>6711978</v>
+        <v>6711864</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5492,32 +5483,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125687091</v>
+        <v>125687090</v>
       </c>
       <c r="B45" t="n">
-        <v>91220</v>
+        <v>91192</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5527,10 +5518,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577156</v>
+        <v>577215</v>
       </c>
       <c r="R45" t="n">
-        <v>6711864</v>
+        <v>6711829</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5589,10 +5580,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125687090</v>
+        <v>125687151</v>
       </c>
       <c r="B46" t="n">
-        <v>91185</v>
+        <v>5176</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5600,34 +5591,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577215</v>
+        <v>577176</v>
       </c>
       <c r="R46" t="n">
-        <v>6711829</v>
+        <v>6711840</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5686,38 +5682,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125687151</v>
+        <v>125687145</v>
       </c>
       <c r="B47" t="n">
-        <v>5176</v>
+        <v>98331</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5726,10 +5726,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577176</v>
+        <v>577155</v>
       </c>
       <c r="R47" t="n">
-        <v>6711840</v>
+        <v>6711978</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5791,7 +5791,7 @@
         <v>125687081</v>
       </c>
       <c r="B48" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>125687133</v>
       </c>
       <c r="B49" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5996,54 +5996,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125687131</v>
+        <v>125687082</v>
       </c>
       <c r="B50" t="n">
-        <v>98324</v>
+        <v>96584</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577148</v>
+        <v>577110</v>
       </c>
       <c r="R50" t="n">
-        <v>6711976</v>
+        <v>6711911</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6102,45 +6093,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125687152</v>
+        <v>125687131</v>
       </c>
       <c r="B51" t="n">
-        <v>102553</v>
+        <v>98331</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>223246</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577131</v>
+        <v>577148</v>
       </c>
       <c r="R51" t="n">
-        <v>6711836</v>
+        <v>6711976</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6175,18 +6175,12 @@
           <t>2025-06-04</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>12 cm dbh</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6205,32 +6199,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125687082</v>
+        <v>125687152</v>
       </c>
       <c r="B52" t="n">
-        <v>96577</v>
+        <v>102560</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>223246</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6240,10 +6234,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577110</v>
+        <v>577131</v>
       </c>
       <c r="R52" t="n">
-        <v>6711911</v>
+        <v>6711836</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6278,12 +6272,18 @@
           <t>2025-06-04</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>12 cm dbh</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6305,7 +6305,7 @@
         <v>125687149</v>
       </c>
       <c r="B53" t="n">
-        <v>95176</v>
+        <v>95183</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>125687084</v>
       </c>
       <c r="B54" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>125687136</v>
       </c>
       <c r="B55" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>125687139</v>
       </c>
       <c r="B56" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>125687095</v>
       </c>
       <c r="B57" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>125687143</v>
       </c>
       <c r="B58" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>125687085</v>
       </c>
       <c r="B59" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>125687114</v>
       </c>
       <c r="B60" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>125687141</v>
       </c>
       <c r="B61" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>125687144</v>
       </c>
       <c r="B62" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>125687128</v>
       </c>
       <c r="B63" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>125687110</v>
       </c>
       <c r="B64" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>125687113</v>
       </c>
       <c r="B65" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>125687112</v>
       </c>
       <c r="B66" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>125687134</v>
       </c>
       <c r="B67" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>125687124</v>
       </c>
       <c r="B68" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>125687137</v>
       </c>
       <c r="B69" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>125687126</v>
       </c>
       <c r="B70" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>125687129</v>
       </c>
       <c r="B71" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>125687119</v>
       </c>
       <c r="B72" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>125687115</v>
       </c>
       <c r="B73" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>125687120</v>
       </c>
       <c r="B74" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>125687148</v>
       </c>
       <c r="B75" t="n">
-        <v>98241</v>
+        <v>98248</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>125687125</v>
       </c>
       <c r="B76" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>125687096</v>
       </c>
       <c r="B77" t="n">
-        <v>103755</v>
+        <v>103762</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>125687087</v>
       </c>
       <c r="B78" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9011,54 +9011,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125687146</v>
+        <v>125687088</v>
       </c>
       <c r="B79" t="n">
-        <v>98324</v>
+        <v>96584</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>577165</v>
+        <v>577173</v>
       </c>
       <c r="R79" t="n">
-        <v>6711956</v>
+        <v>6711943</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9117,45 +9108,50 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125687088</v>
+        <v>125687097</v>
       </c>
       <c r="B80" t="n">
-        <v>96577</v>
+        <v>4772</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>577173</v>
+        <v>577154</v>
       </c>
       <c r="R80" t="n">
-        <v>6711943</v>
+        <v>6711917</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9214,38 +9210,42 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125687097</v>
+        <v>125687146</v>
       </c>
       <c r="B81" t="n">
-        <v>4772</v>
+        <v>98331</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9254,10 +9254,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>577154</v>
+        <v>577165</v>
       </c>
       <c r="R81" t="n">
-        <v>6711917</v>
+        <v>6711956</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9319,7 +9319,7 @@
         <v>125687094</v>
       </c>
       <c r="B82" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>125687132</v>
       </c>
       <c r="B83" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>125687117</v>
       </c>
       <c r="B84" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>125687118</v>
       </c>
       <c r="B85" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>125687135</v>
       </c>
       <c r="B86" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -4869,38 +4869,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125687150</v>
+        <v>125687122</v>
       </c>
       <c r="B39" t="n">
-        <v>5176</v>
+        <v>98331</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4909,10 +4913,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577174</v>
+        <v>577145</v>
       </c>
       <c r="R39" t="n">
-        <v>6711873</v>
+        <v>6711917</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4971,7 +4975,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125687122</v>
+        <v>125687130</v>
       </c>
       <c r="B40" t="n">
         <v>98331</v>
@@ -5001,7 +5005,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5015,10 +5019,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577145</v>
+        <v>577105</v>
       </c>
       <c r="R40" t="n">
-        <v>6711917</v>
+        <v>6711976</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5077,7 +5081,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125687130</v>
+        <v>125687140</v>
       </c>
       <c r="B41" t="n">
         <v>98331</v>
@@ -5107,7 +5111,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5121,10 +5125,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577105</v>
+        <v>577141</v>
       </c>
       <c r="R41" t="n">
-        <v>6711976</v>
+        <v>6711960</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5183,42 +5187,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125687140</v>
+        <v>125687150</v>
       </c>
       <c r="B42" t="n">
-        <v>98331</v>
+        <v>5176</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577141</v>
+        <v>577174</v>
       </c>
       <c r="R42" t="n">
-        <v>6711960</v>
+        <v>6711873</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5788,45 +5788,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125687081</v>
+        <v>125687133</v>
       </c>
       <c r="B48" t="n">
-        <v>96584</v>
+        <v>98331</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577109</v>
+        <v>577171</v>
       </c>
       <c r="R48" t="n">
-        <v>6711890</v>
+        <v>6711869</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5859,6 +5868,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5885,54 +5899,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125687133</v>
+        <v>125687081</v>
       </c>
       <c r="B49" t="n">
-        <v>98331</v>
+        <v>96584</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577171</v>
+        <v>577109</v>
       </c>
       <c r="R49" t="n">
-        <v>6711869</v>
+        <v>6711890</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5965,11 +5970,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -4869,42 +4869,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125687122</v>
+        <v>125687150</v>
       </c>
       <c r="B39" t="n">
-        <v>98331</v>
+        <v>5176</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4913,10 +4909,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577145</v>
+        <v>577174</v>
       </c>
       <c r="R39" t="n">
-        <v>6711917</v>
+        <v>6711873</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4975,7 +4971,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125687130</v>
+        <v>125687122</v>
       </c>
       <c r="B40" t="n">
         <v>98331</v>
@@ -5005,7 +5001,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5019,10 +5015,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577105</v>
+        <v>577145</v>
       </c>
       <c r="R40" t="n">
-        <v>6711976</v>
+        <v>6711917</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5081,7 +5077,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125687140</v>
+        <v>125687130</v>
       </c>
       <c r="B41" t="n">
         <v>98331</v>
@@ -5111,7 +5107,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5125,10 +5121,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577141</v>
+        <v>577105</v>
       </c>
       <c r="R41" t="n">
-        <v>6711960</v>
+        <v>6711976</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5187,38 +5183,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125687150</v>
+        <v>125687140</v>
       </c>
       <c r="B42" t="n">
-        <v>5176</v>
+        <v>98331</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577174</v>
+        <v>577141</v>
       </c>
       <c r="R42" t="n">
-        <v>6711873</v>
+        <v>6711960</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5788,54 +5788,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125687133</v>
+        <v>125687081</v>
       </c>
       <c r="B48" t="n">
-        <v>98331</v>
+        <v>96584</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577171</v>
+        <v>577109</v>
       </c>
       <c r="R48" t="n">
-        <v>6711869</v>
+        <v>6711890</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5868,11 +5859,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5899,45 +5885,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125687081</v>
+        <v>125687133</v>
       </c>
       <c r="B49" t="n">
-        <v>96584</v>
+        <v>98331</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577109</v>
+        <v>577171</v>
       </c>
       <c r="R49" t="n">
-        <v>6711890</v>
+        <v>6711869</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5970,6 +5965,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7114,7 +7114,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125687141</v>
+        <v>125687113</v>
       </c>
       <c r="B61" t="n">
         <v>98331</v>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>577143</v>
+        <v>577142</v>
       </c>
       <c r="R61" t="n">
-        <v>6711958</v>
+        <v>6711971</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7220,7 +7220,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125687144</v>
+        <v>125687141</v>
       </c>
       <c r="B62" t="n">
         <v>98331</v>
@@ -7264,10 +7264,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577150</v>
+        <v>577143</v>
       </c>
       <c r="R62" t="n">
-        <v>6711962</v>
+        <v>6711958</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7326,7 +7326,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125687128</v>
+        <v>125687144</v>
       </c>
       <c r="B63" t="n">
         <v>98331</v>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577194</v>
+        <v>577150</v>
       </c>
       <c r="R63" t="n">
-        <v>6711897</v>
+        <v>6711962</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7432,7 +7432,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125687110</v>
+        <v>125687128</v>
       </c>
       <c r="B64" t="n">
         <v>98331</v>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7470,23 +7470,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>577101</v>
+        <v>577194</v>
       </c>
       <c r="R64" t="n">
-        <v>6711989</v>
+        <v>6711897</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7527,7 +7520,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7546,7 +7538,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125687113</v>
+        <v>125687110</v>
       </c>
       <c r="B65" t="n">
         <v>98331</v>
@@ -7576,7 +7568,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7584,16 +7576,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>577142</v>
+        <v>577101</v>
       </c>
       <c r="R65" t="n">
-        <v>6711971</v>
+        <v>6711989</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7634,6 +7633,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -9108,38 +9108,42 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125687097</v>
+        <v>125687146</v>
       </c>
       <c r="B80" t="n">
-        <v>4772</v>
+        <v>98331</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9148,10 +9152,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>577154</v>
+        <v>577165</v>
       </c>
       <c r="R80" t="n">
-        <v>6711917</v>
+        <v>6711956</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9210,42 +9214,38 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125687146</v>
+        <v>125687097</v>
       </c>
       <c r="B81" t="n">
-        <v>98331</v>
+        <v>4772</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9254,10 +9254,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>577165</v>
+        <v>577154</v>
       </c>
       <c r="R81" t="n">
-        <v>6711956</v>
+        <v>6711917</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -3622,7 +3622,7 @@
         <v>125512020</v>
       </c>
       <c r="B27" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>125687083</v>
       </c>
       <c r="B28" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>125687078</v>
       </c>
       <c r="B29" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>125687111</v>
       </c>
       <c r="B30" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>125687079</v>
       </c>
       <c r="B31" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>125687142</v>
       </c>
       <c r="B32" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>125687123</v>
       </c>
       <c r="B33" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>125687116</v>
       </c>
       <c r="B34" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>125687086</v>
       </c>
       <c r="B35" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>125687121</v>
       </c>
       <c r="B36" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>125687127</v>
       </c>
       <c r="B37" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>125687092</v>
       </c>
       <c r="B38" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>125687122</v>
       </c>
       <c r="B40" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>125687130</v>
       </c>
       <c r="B41" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>125687140</v>
       </c>
       <c r="B42" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>125687093</v>
       </c>
       <c r="B43" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>125687091</v>
       </c>
       <c r="B44" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5483,10 +5483,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125687090</v>
+        <v>125687151</v>
       </c>
       <c r="B45" t="n">
-        <v>91192</v>
+        <v>5176</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5494,34 +5494,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577215</v>
+        <v>577176</v>
       </c>
       <c r="R45" t="n">
-        <v>6711829</v>
+        <v>6711840</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5580,38 +5585,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125687151</v>
+        <v>125687145</v>
       </c>
       <c r="B46" t="n">
-        <v>5176</v>
+        <v>98334</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5620,10 +5629,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577176</v>
+        <v>577155</v>
       </c>
       <c r="R46" t="n">
-        <v>6711840</v>
+        <v>6711978</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5682,54 +5691,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125687145</v>
+        <v>125687090</v>
       </c>
       <c r="B47" t="n">
-        <v>98331</v>
+        <v>91193</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577155</v>
+        <v>577215</v>
       </c>
       <c r="R47" t="n">
-        <v>6711978</v>
+        <v>6711829</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5791,7 +5791,7 @@
         <v>125687081</v>
       </c>
       <c r="B48" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>125687133</v>
       </c>
       <c r="B49" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5996,32 +5996,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125687082</v>
+        <v>125687152</v>
       </c>
       <c r="B50" t="n">
-        <v>96584</v>
+        <v>102563</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>223246</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577110</v>
+        <v>577131</v>
       </c>
       <c r="R50" t="n">
-        <v>6711911</v>
+        <v>6711836</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6069,12 +6069,18 @@
           <t>2025-06-04</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>12 cm dbh</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6093,54 +6099,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125687131</v>
+        <v>125687082</v>
       </c>
       <c r="B51" t="n">
-        <v>98331</v>
+        <v>96587</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577148</v>
+        <v>577110</v>
       </c>
       <c r="R51" t="n">
-        <v>6711976</v>
+        <v>6711911</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6199,45 +6196,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125687152</v>
+        <v>125687131</v>
       </c>
       <c r="B52" t="n">
-        <v>102560</v>
+        <v>98334</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>223246</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577131</v>
+        <v>577148</v>
       </c>
       <c r="R52" t="n">
-        <v>6711836</v>
+        <v>6711976</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6272,18 +6278,12 @@
           <t>2025-06-04</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>12 cm dbh</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6305,7 +6305,7 @@
         <v>125687149</v>
       </c>
       <c r="B53" t="n">
-        <v>95183</v>
+        <v>95186</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>125687084</v>
       </c>
       <c r="B54" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>125687136</v>
       </c>
       <c r="B55" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>125687139</v>
       </c>
       <c r="B56" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>125687095</v>
       </c>
       <c r="B57" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>125687143</v>
       </c>
       <c r="B58" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6911,45 +6911,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125687085</v>
+        <v>125687114</v>
       </c>
       <c r="B59" t="n">
-        <v>96584</v>
+        <v>98334</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>577130</v>
+        <v>577145</v>
       </c>
       <c r="R59" t="n">
-        <v>6711985</v>
+        <v>6711974</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7008,54 +7017,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125687114</v>
+        <v>125687085</v>
       </c>
       <c r="B60" t="n">
-        <v>98331</v>
+        <v>96587</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577145</v>
+        <v>577130</v>
       </c>
       <c r="R60" t="n">
-        <v>6711974</v>
+        <v>6711985</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7114,10 +7114,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125687113</v>
+        <v>125687141</v>
       </c>
       <c r="B61" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>577142</v>
+        <v>577143</v>
       </c>
       <c r="R61" t="n">
-        <v>6711971</v>
+        <v>6711958</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7220,10 +7220,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125687141</v>
+        <v>125687144</v>
       </c>
       <c r="B62" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7264,10 +7264,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577143</v>
+        <v>577150</v>
       </c>
       <c r="R62" t="n">
-        <v>6711958</v>
+        <v>6711962</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7326,10 +7326,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125687144</v>
+        <v>125687128</v>
       </c>
       <c r="B63" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577150</v>
+        <v>577194</v>
       </c>
       <c r="R63" t="n">
-        <v>6711962</v>
+        <v>6711897</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7432,10 +7432,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125687128</v>
+        <v>125687110</v>
       </c>
       <c r="B64" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7470,16 +7470,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>577194</v>
+        <v>577101</v>
       </c>
       <c r="R64" t="n">
-        <v>6711897</v>
+        <v>6711989</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7520,6 +7527,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7538,10 +7546,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125687110</v>
+        <v>125687113</v>
       </c>
       <c r="B65" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7568,7 +7576,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7576,23 +7584,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>577101</v>
+        <v>577142</v>
       </c>
       <c r="R65" t="n">
-        <v>6711989</v>
+        <v>6711971</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7633,7 +7634,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7655,7 +7655,7 @@
         <v>125687112</v>
       </c>
       <c r="B66" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>125687134</v>
       </c>
       <c r="B67" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>125687124</v>
       </c>
       <c r="B68" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>125687137</v>
       </c>
       <c r="B69" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>125687126</v>
       </c>
       <c r="B70" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>125687129</v>
       </c>
       <c r="B71" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>125687119</v>
       </c>
       <c r="B72" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>125687115</v>
       </c>
       <c r="B73" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>125687120</v>
       </c>
       <c r="B74" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8614,32 +8614,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125687148</v>
+        <v>125687087</v>
       </c>
       <c r="B75" t="n">
-        <v>98248</v>
+        <v>96587</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219790</v>
+        <v>53</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>577163</v>
+        <v>577157</v>
       </c>
       <c r="R75" t="n">
-        <v>6711969</v>
+        <v>6711975</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8711,54 +8711,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125687125</v>
+        <v>125687148</v>
       </c>
       <c r="B76" t="n">
-        <v>98331</v>
+        <v>98251</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>577172</v>
+        <v>577163</v>
       </c>
       <c r="R76" t="n">
-        <v>6711942</v>
+        <v>6711969</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8817,45 +8808,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125687096</v>
+        <v>125687125</v>
       </c>
       <c r="B77" t="n">
-        <v>103762</v>
+        <v>98334</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>577145</v>
+        <v>577172</v>
       </c>
       <c r="R77" t="n">
-        <v>6711831</v>
+        <v>6711942</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8914,32 +8914,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125687087</v>
+        <v>125687096</v>
       </c>
       <c r="B78" t="n">
-        <v>96584</v>
+        <v>103765</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>222412</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8949,10 +8949,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>577157</v>
+        <v>577145</v>
       </c>
       <c r="R78" t="n">
-        <v>6711975</v>
+        <v>6711831</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9014,7 +9014,7 @@
         <v>125687088</v>
       </c>
       <c r="B79" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9108,42 +9108,38 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125687146</v>
+        <v>125687097</v>
       </c>
       <c r="B80" t="n">
-        <v>98331</v>
+        <v>4772</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9152,10 +9148,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>577165</v>
+        <v>577154</v>
       </c>
       <c r="R80" t="n">
-        <v>6711956</v>
+        <v>6711917</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9214,38 +9210,42 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125687097</v>
+        <v>125687146</v>
       </c>
       <c r="B81" t="n">
-        <v>4772</v>
+        <v>98334</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9254,10 +9254,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>577154</v>
+        <v>577165</v>
       </c>
       <c r="R81" t="n">
-        <v>6711917</v>
+        <v>6711956</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9319,7 +9319,7 @@
         <v>125687094</v>
       </c>
       <c r="B82" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9413,10 +9413,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125687132</v>
+        <v>125687117</v>
       </c>
       <c r="B83" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>577153</v>
+        <v>577124</v>
       </c>
       <c r="R83" t="n">
         <v>6711978</v>
@@ -9519,10 +9519,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125687117</v>
+        <v>125687132</v>
       </c>
       <c r="B84" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>577124</v>
+        <v>577153</v>
       </c>
       <c r="R84" t="n">
         <v>6711978</v>
@@ -9628,7 +9628,7 @@
         <v>125687118</v>
       </c>
       <c r="B85" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>125687135</v>
       </c>
       <c r="B86" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -5483,10 +5483,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125687151</v>
+        <v>125687090</v>
       </c>
       <c r="B45" t="n">
-        <v>5176</v>
+        <v>91193</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5494,39 +5494,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577176</v>
+        <v>577215</v>
       </c>
       <c r="R45" t="n">
-        <v>6711840</v>
+        <v>6711829</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5585,42 +5580,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125687145</v>
+        <v>125687151</v>
       </c>
       <c r="B46" t="n">
-        <v>98334</v>
+        <v>5176</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5629,10 +5620,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577155</v>
+        <v>577176</v>
       </c>
       <c r="R46" t="n">
-        <v>6711978</v>
+        <v>6711840</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5691,45 +5682,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125687090</v>
+        <v>125687145</v>
       </c>
       <c r="B47" t="n">
-        <v>91193</v>
+        <v>98334</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577215</v>
+        <v>577155</v>
       </c>
       <c r="R47" t="n">
-        <v>6711829</v>
+        <v>6711978</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6708,45 +6708,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125687095</v>
+        <v>125687143</v>
       </c>
       <c r="B57" t="n">
-        <v>91228</v>
+        <v>98334</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>577135</v>
+        <v>577152</v>
       </c>
       <c r="R57" t="n">
-        <v>6711824</v>
+        <v>6711960</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6805,54 +6814,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125687143</v>
+        <v>125687095</v>
       </c>
       <c r="B58" t="n">
-        <v>98334</v>
+        <v>91228</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>577152</v>
+        <v>577135</v>
       </c>
       <c r="R58" t="n">
-        <v>6711960</v>
+        <v>6711824</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -9413,7 +9413,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125687117</v>
+        <v>125687132</v>
       </c>
       <c r="B83" t="n">
         <v>98334</v>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>577124</v>
+        <v>577153</v>
       </c>
       <c r="R83" t="n">
         <v>6711978</v>
@@ -9519,7 +9519,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125687132</v>
+        <v>125687117</v>
       </c>
       <c r="B84" t="n">
         <v>98334</v>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>577153</v>
+        <v>577124</v>
       </c>
       <c r="R84" t="n">
         <v>6711978</v>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -3622,7 +3622,7 @@
         <v>125512020</v>
       </c>
       <c r="B27" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>125687083</v>
       </c>
       <c r="B28" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>125687078</v>
       </c>
       <c r="B29" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>125687111</v>
       </c>
       <c r="B30" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>125687079</v>
       </c>
       <c r="B31" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>125687142</v>
       </c>
       <c r="B32" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>125687123</v>
       </c>
       <c r="B33" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>125687116</v>
       </c>
       <c r="B34" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>125687086</v>
       </c>
       <c r="B35" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>125687121</v>
       </c>
       <c r="B36" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>125687127</v>
       </c>
       <c r="B37" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4772,45 +4772,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125687092</v>
+        <v>125687150</v>
       </c>
       <c r="B38" t="n">
-        <v>91228</v>
+        <v>5176</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577169</v>
+        <v>577174</v>
       </c>
       <c r="R38" t="n">
-        <v>6711859</v>
+        <v>6711873</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4869,38 +4874,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125687150</v>
+        <v>125687122</v>
       </c>
       <c r="B39" t="n">
-        <v>5176</v>
+        <v>98338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4909,10 +4918,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577174</v>
+        <v>577145</v>
       </c>
       <c r="R39" t="n">
-        <v>6711873</v>
+        <v>6711917</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4971,10 +4980,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125687122</v>
+        <v>125687130</v>
       </c>
       <c r="B40" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5001,7 +5010,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5015,10 +5024,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577145</v>
+        <v>577105</v>
       </c>
       <c r="R40" t="n">
-        <v>6711917</v>
+        <v>6711976</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5077,10 +5086,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125687130</v>
+        <v>125687140</v>
       </c>
       <c r="B41" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5107,7 +5116,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5121,10 +5130,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577105</v>
+        <v>577141</v>
       </c>
       <c r="R41" t="n">
-        <v>6711976</v>
+        <v>6711960</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5183,54 +5192,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125687140</v>
+        <v>125687092</v>
       </c>
       <c r="B42" t="n">
-        <v>98334</v>
+        <v>91232</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577141</v>
+        <v>577169</v>
       </c>
       <c r="R42" t="n">
-        <v>6711960</v>
+        <v>6711859</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5289,45 +5289,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125687093</v>
+        <v>125687145</v>
       </c>
       <c r="B43" t="n">
-        <v>91228</v>
+        <v>98338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577243</v>
+        <v>577155</v>
       </c>
       <c r="R43" t="n">
-        <v>6711783</v>
+        <v>6711978</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5386,45 +5395,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125687091</v>
+        <v>125687151</v>
       </c>
       <c r="B44" t="n">
-        <v>91228</v>
+        <v>5176</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577156</v>
+        <v>577176</v>
       </c>
       <c r="R44" t="n">
-        <v>6711864</v>
+        <v>6711840</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5483,32 +5497,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125687090</v>
+        <v>125687093</v>
       </c>
       <c r="B45" t="n">
-        <v>91193</v>
+        <v>91232</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5518,10 +5532,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577215</v>
+        <v>577243</v>
       </c>
       <c r="R45" t="n">
-        <v>6711829</v>
+        <v>6711783</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5580,50 +5594,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125687151</v>
+        <v>125687091</v>
       </c>
       <c r="B46" t="n">
-        <v>5176</v>
+        <v>91232</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577176</v>
+        <v>577156</v>
       </c>
       <c r="R46" t="n">
-        <v>6711840</v>
+        <v>6711864</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5682,54 +5691,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125687145</v>
+        <v>125687090</v>
       </c>
       <c r="B47" t="n">
-        <v>98334</v>
+        <v>91197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577155</v>
+        <v>577215</v>
       </c>
       <c r="R47" t="n">
-        <v>6711978</v>
+        <v>6711829</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5788,45 +5788,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125687081</v>
+        <v>125687133</v>
       </c>
       <c r="B48" t="n">
-        <v>96587</v>
+        <v>98338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577109</v>
+        <v>577171</v>
       </c>
       <c r="R48" t="n">
-        <v>6711890</v>
+        <v>6711869</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5859,6 +5868,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5885,54 +5899,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125687133</v>
+        <v>125687081</v>
       </c>
       <c r="B49" t="n">
-        <v>98334</v>
+        <v>96591</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577171</v>
+        <v>577109</v>
       </c>
       <c r="R49" t="n">
-        <v>6711869</v>
+        <v>6711890</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5965,11 +5970,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5999,7 +5999,7 @@
         <v>125687152</v>
       </c>
       <c r="B50" t="n">
-        <v>102563</v>
+        <v>102567</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>125687082</v>
       </c>
       <c r="B51" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>125687131</v>
       </c>
       <c r="B52" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>125687149</v>
       </c>
       <c r="B53" t="n">
-        <v>95186</v>
+        <v>95190</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>125687084</v>
       </c>
       <c r="B54" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>125687136</v>
       </c>
       <c r="B55" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>125687139</v>
       </c>
       <c r="B56" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6708,54 +6708,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125687143</v>
+        <v>125687095</v>
       </c>
       <c r="B57" t="n">
-        <v>98334</v>
+        <v>91232</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>577152</v>
+        <v>577135</v>
       </c>
       <c r="R57" t="n">
-        <v>6711960</v>
+        <v>6711824</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6814,45 +6805,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125687095</v>
+        <v>125687143</v>
       </c>
       <c r="B58" t="n">
-        <v>91228</v>
+        <v>98338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>577135</v>
+        <v>577152</v>
       </c>
       <c r="R58" t="n">
-        <v>6711824</v>
+        <v>6711960</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6911,54 +6911,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125687114</v>
+        <v>125687085</v>
       </c>
       <c r="B59" t="n">
-        <v>98334</v>
+        <v>96591</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>577145</v>
+        <v>577130</v>
       </c>
       <c r="R59" t="n">
-        <v>6711974</v>
+        <v>6711985</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7017,45 +7008,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125687085</v>
+        <v>125687114</v>
       </c>
       <c r="B60" t="n">
-        <v>96587</v>
+        <v>98338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577130</v>
+        <v>577145</v>
       </c>
       <c r="R60" t="n">
-        <v>6711985</v>
+        <v>6711974</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7117,7 +7117,7 @@
         <v>125687141</v>
       </c>
       <c r="B61" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>125687144</v>
       </c>
       <c r="B62" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>125687128</v>
       </c>
       <c r="B63" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>125687110</v>
       </c>
       <c r="B64" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>125687113</v>
       </c>
       <c r="B65" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>125687112</v>
       </c>
       <c r="B66" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>125687134</v>
       </c>
       <c r="B67" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>125687124</v>
       </c>
       <c r="B68" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>125687137</v>
       </c>
       <c r="B69" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>125687126</v>
       </c>
       <c r="B70" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>125687129</v>
       </c>
       <c r="B71" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>125687119</v>
       </c>
       <c r="B72" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>125687115</v>
       </c>
       <c r="B73" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>125687120</v>
       </c>
       <c r="B74" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8614,32 +8614,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125687087</v>
+        <v>125687096</v>
       </c>
       <c r="B75" t="n">
-        <v>96587</v>
+        <v>103769</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>53</v>
+        <v>222412</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>577157</v>
+        <v>577145</v>
       </c>
       <c r="R75" t="n">
-        <v>6711975</v>
+        <v>6711831</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8714,7 +8714,7 @@
         <v>125687148</v>
       </c>
       <c r="B76" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>125687125</v>
       </c>
       <c r="B77" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8914,32 +8914,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125687096</v>
+        <v>125687087</v>
       </c>
       <c r="B78" t="n">
-        <v>103765</v>
+        <v>96591</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8949,10 +8949,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>577145</v>
+        <v>577157</v>
       </c>
       <c r="R78" t="n">
-        <v>6711831</v>
+        <v>6711975</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9011,45 +9011,50 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125687088</v>
+        <v>125687097</v>
       </c>
       <c r="B79" t="n">
-        <v>96587</v>
+        <v>4772</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>577173</v>
+        <v>577154</v>
       </c>
       <c r="R79" t="n">
-        <v>6711943</v>
+        <v>6711917</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9108,38 +9113,42 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125687097</v>
+        <v>125687146</v>
       </c>
       <c r="B80" t="n">
-        <v>4772</v>
+        <v>98338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9148,10 +9157,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>577154</v>
+        <v>577165</v>
       </c>
       <c r="R80" t="n">
-        <v>6711917</v>
+        <v>6711956</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9210,54 +9219,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125687146</v>
+        <v>125687088</v>
       </c>
       <c r="B81" t="n">
-        <v>98334</v>
+        <v>96591</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>577165</v>
+        <v>577173</v>
       </c>
       <c r="R81" t="n">
-        <v>6711956</v>
+        <v>6711943</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9319,7 +9319,7 @@
         <v>125687094</v>
       </c>
       <c r="B82" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>125687132</v>
       </c>
       <c r="B83" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>125687117</v>
       </c>
       <c r="B84" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>125687118</v>
       </c>
       <c r="B85" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>125687135</v>
       </c>
       <c r="B86" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -4040,45 +4040,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125687079</v>
+        <v>125687142</v>
       </c>
       <c r="B31" t="n">
-        <v>96591</v>
+        <v>98338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577171</v>
+        <v>577150</v>
       </c>
       <c r="R31" t="n">
-        <v>6711847</v>
+        <v>6711955</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4137,7 +4146,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125687142</v>
+        <v>125687123</v>
       </c>
       <c r="B32" t="n">
         <v>98338</v>
@@ -4167,7 +4176,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4181,10 +4190,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577150</v>
+        <v>577090</v>
       </c>
       <c r="R32" t="n">
-        <v>6711955</v>
+        <v>6711978</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4243,7 +4252,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125687123</v>
+        <v>125687116</v>
       </c>
       <c r="B33" t="n">
         <v>98338</v>
@@ -4273,7 +4282,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4287,10 +4296,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577090</v>
+        <v>577202</v>
       </c>
       <c r="R33" t="n">
-        <v>6711978</v>
+        <v>6711890</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4349,54 +4358,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125687116</v>
+        <v>125687079</v>
       </c>
       <c r="B34" t="n">
-        <v>98338</v>
+        <v>96591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577202</v>
+        <v>577171</v>
       </c>
       <c r="R34" t="n">
-        <v>6711890</v>
+        <v>6711847</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5289,42 +5289,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125687145</v>
+        <v>125687151</v>
       </c>
       <c r="B43" t="n">
-        <v>98338</v>
+        <v>5176</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5333,10 +5329,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577155</v>
+        <v>577176</v>
       </c>
       <c r="R43" t="n">
-        <v>6711978</v>
+        <v>6711840</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5395,50 +5391,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125687151</v>
+        <v>125687093</v>
       </c>
       <c r="B44" t="n">
-        <v>5176</v>
+        <v>91232</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577176</v>
+        <v>577243</v>
       </c>
       <c r="R44" t="n">
-        <v>6711840</v>
+        <v>6711783</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5497,7 +5488,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125687093</v>
+        <v>125687091</v>
       </c>
       <c r="B45" t="n">
         <v>91232</v>
@@ -5532,10 +5523,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577243</v>
+        <v>577156</v>
       </c>
       <c r="R45" t="n">
-        <v>6711783</v>
+        <v>6711864</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5594,32 +5585,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125687091</v>
+        <v>125687090</v>
       </c>
       <c r="B46" t="n">
-        <v>91232</v>
+        <v>91197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5629,10 +5620,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577156</v>
+        <v>577215</v>
       </c>
       <c r="R46" t="n">
-        <v>6711864</v>
+        <v>6711829</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5691,45 +5682,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125687090</v>
+        <v>125687145</v>
       </c>
       <c r="B47" t="n">
-        <v>91197</v>
+        <v>98338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577215</v>
+        <v>577155</v>
       </c>
       <c r="R47" t="n">
-        <v>6711829</v>
+        <v>6711978</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5788,54 +5788,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125687133</v>
+        <v>125687081</v>
       </c>
       <c r="B48" t="n">
-        <v>98338</v>
+        <v>96591</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577171</v>
+        <v>577109</v>
       </c>
       <c r="R48" t="n">
-        <v>6711869</v>
+        <v>6711890</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5868,11 +5859,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5899,45 +5885,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125687081</v>
+        <v>125687133</v>
       </c>
       <c r="B49" t="n">
-        <v>96591</v>
+        <v>98338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577109</v>
+        <v>577171</v>
       </c>
       <c r="R49" t="n">
-        <v>6711890</v>
+        <v>6711869</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5970,6 +5965,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5996,32 +5996,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125687152</v>
+        <v>125687082</v>
       </c>
       <c r="B50" t="n">
-        <v>102567</v>
+        <v>96591</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>223246</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577131</v>
+        <v>577110</v>
       </c>
       <c r="R50" t="n">
-        <v>6711836</v>
+        <v>6711911</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6069,18 +6069,12 @@
           <t>2025-06-04</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>12 cm dbh</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6099,45 +6093,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125687082</v>
+        <v>125687131</v>
       </c>
       <c r="B51" t="n">
-        <v>96591</v>
+        <v>98338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577110</v>
+        <v>577148</v>
       </c>
       <c r="R51" t="n">
-        <v>6711911</v>
+        <v>6711976</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6196,54 +6199,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125687131</v>
+        <v>125687152</v>
       </c>
       <c r="B52" t="n">
-        <v>98338</v>
+        <v>102567</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>223246</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577148</v>
+        <v>577131</v>
       </c>
       <c r="R52" t="n">
-        <v>6711976</v>
+        <v>6711836</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6278,12 +6272,18 @@
           <t>2025-06-04</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>12 cm dbh</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -3622,7 +3622,7 @@
         <v>125512020</v>
       </c>
       <c r="B27" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3740,45 +3740,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125687083</v>
+        <v>125687111</v>
       </c>
       <c r="B28" t="n">
-        <v>96591</v>
+        <v>98339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577154</v>
+        <v>577182</v>
       </c>
       <c r="R28" t="n">
-        <v>6711905</v>
+        <v>6711920</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3837,10 +3846,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125687078</v>
+        <v>125687083</v>
       </c>
       <c r="B29" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3872,10 +3881,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577169</v>
+        <v>577154</v>
       </c>
       <c r="R29" t="n">
-        <v>6711894</v>
+        <v>6711905</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3934,54 +3943,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125687111</v>
+        <v>125687078</v>
       </c>
       <c r="B30" t="n">
-        <v>98338</v>
+        <v>96592</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577182</v>
+        <v>577169</v>
       </c>
       <c r="R30" t="n">
-        <v>6711920</v>
+        <v>6711894</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4040,10 +4040,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125687142</v>
+        <v>125687116</v>
       </c>
       <c r="B31" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4084,10 +4084,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577150</v>
+        <v>577202</v>
       </c>
       <c r="R31" t="n">
-        <v>6711955</v>
+        <v>6711890</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4146,10 +4146,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125687123</v>
+        <v>125687142</v>
       </c>
       <c r="B32" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4190,10 +4190,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577090</v>
+        <v>577150</v>
       </c>
       <c r="R32" t="n">
-        <v>6711978</v>
+        <v>6711955</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4252,10 +4252,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125687116</v>
+        <v>125687123</v>
       </c>
       <c r="B33" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577202</v>
+        <v>577090</v>
       </c>
       <c r="R33" t="n">
-        <v>6711890</v>
+        <v>6711978</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4361,7 +4361,7 @@
         <v>125687079</v>
       </c>
       <c r="B34" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>125687086</v>
       </c>
       <c r="B35" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>125687121</v>
       </c>
       <c r="B36" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>125687127</v>
       </c>
       <c r="B37" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4772,50 +4772,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125687150</v>
+        <v>125687092</v>
       </c>
       <c r="B38" t="n">
-        <v>5176</v>
+        <v>91232</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577174</v>
+        <v>577169</v>
       </c>
       <c r="R38" t="n">
-        <v>6711873</v>
+        <v>6711859</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4874,10 +4869,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125687122</v>
+        <v>125687130</v>
       </c>
       <c r="B39" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4904,7 +4899,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4918,10 +4913,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577145</v>
+        <v>577105</v>
       </c>
       <c r="R39" t="n">
-        <v>6711917</v>
+        <v>6711976</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4980,10 +4975,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125687130</v>
+        <v>125687122</v>
       </c>
       <c r="B40" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5010,7 +5005,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5024,10 +5019,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577105</v>
+        <v>577145</v>
       </c>
       <c r="R40" t="n">
-        <v>6711976</v>
+        <v>6711917</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5089,7 +5084,7 @@
         <v>125687140</v>
       </c>
       <c r="B41" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5192,45 +5187,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125687092</v>
+        <v>125687150</v>
       </c>
       <c r="B42" t="n">
-        <v>91232</v>
+        <v>5176</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577169</v>
+        <v>577174</v>
       </c>
       <c r="R42" t="n">
-        <v>6711859</v>
+        <v>6711873</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5289,38 +5289,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125687151</v>
+        <v>125687145</v>
       </c>
       <c r="B43" t="n">
-        <v>5176</v>
+        <v>98339</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5329,10 +5333,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577176</v>
+        <v>577155</v>
       </c>
       <c r="R43" t="n">
-        <v>6711840</v>
+        <v>6711978</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5391,32 +5395,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125687093</v>
+        <v>125687090</v>
       </c>
       <c r="B44" t="n">
-        <v>91232</v>
+        <v>91197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5426,10 +5430,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577243</v>
+        <v>577215</v>
       </c>
       <c r="R44" t="n">
-        <v>6711783</v>
+        <v>6711829</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5488,7 +5492,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125687091</v>
+        <v>125687093</v>
       </c>
       <c r="B45" t="n">
         <v>91232</v>
@@ -5523,10 +5527,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577156</v>
+        <v>577243</v>
       </c>
       <c r="R45" t="n">
-        <v>6711864</v>
+        <v>6711783</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5585,32 +5589,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125687090</v>
+        <v>125687091</v>
       </c>
       <c r="B46" t="n">
-        <v>91197</v>
+        <v>91232</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5620,10 +5624,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577215</v>
+        <v>577156</v>
       </c>
       <c r="R46" t="n">
-        <v>6711829</v>
+        <v>6711864</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5682,42 +5686,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125687145</v>
+        <v>125687151</v>
       </c>
       <c r="B47" t="n">
-        <v>98338</v>
+        <v>5176</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5726,10 +5726,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577155</v>
+        <v>577176</v>
       </c>
       <c r="R47" t="n">
-        <v>6711978</v>
+        <v>6711840</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5788,45 +5788,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125687081</v>
+        <v>125687133</v>
       </c>
       <c r="B48" t="n">
-        <v>96591</v>
+        <v>98339</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577109</v>
+        <v>577171</v>
       </c>
       <c r="R48" t="n">
-        <v>6711890</v>
+        <v>6711869</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5859,6 +5868,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5885,54 +5899,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125687133</v>
+        <v>125687081</v>
       </c>
       <c r="B49" t="n">
-        <v>98338</v>
+        <v>96592</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577171</v>
+        <v>577109</v>
       </c>
       <c r="R49" t="n">
-        <v>6711869</v>
+        <v>6711890</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5965,11 +5970,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5996,32 +5996,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125687082</v>
+        <v>125687152</v>
       </c>
       <c r="B50" t="n">
-        <v>96591</v>
+        <v>102568</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>223246</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577110</v>
+        <v>577131</v>
       </c>
       <c r="R50" t="n">
-        <v>6711911</v>
+        <v>6711836</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6069,12 +6069,18 @@
           <t>2025-06-04</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>12 cm dbh</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6093,54 +6099,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125687131</v>
+        <v>125687082</v>
       </c>
       <c r="B51" t="n">
-        <v>98338</v>
+        <v>96592</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577148</v>
+        <v>577110</v>
       </c>
       <c r="R51" t="n">
-        <v>6711976</v>
+        <v>6711911</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6199,45 +6196,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125687152</v>
+        <v>125687131</v>
       </c>
       <c r="B52" t="n">
-        <v>102567</v>
+        <v>98339</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>223246</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577131</v>
+        <v>577148</v>
       </c>
       <c r="R52" t="n">
-        <v>6711836</v>
+        <v>6711976</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6272,18 +6278,12 @@
           <t>2025-06-04</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>12 cm dbh</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6305,7 +6305,7 @@
         <v>125687149</v>
       </c>
       <c r="B53" t="n">
-        <v>95190</v>
+        <v>95191</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>125687084</v>
       </c>
       <c r="B54" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6496,10 +6496,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125687136</v>
+        <v>125687139</v>
       </c>
       <c r="B55" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>577187</v>
+        <v>577090</v>
       </c>
       <c r="R55" t="n">
-        <v>6711916</v>
+        <v>6711973</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6602,10 +6602,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125687139</v>
+        <v>125687136</v>
       </c>
       <c r="B56" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>577090</v>
+        <v>577187</v>
       </c>
       <c r="R56" t="n">
-        <v>6711973</v>
+        <v>6711916</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6808,7 +6808,7 @@
         <v>125687143</v>
       </c>
       <c r="B58" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>125687085</v>
       </c>
       <c r="B59" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>125687114</v>
       </c>
       <c r="B60" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7114,10 +7114,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125687141</v>
+        <v>125687144</v>
       </c>
       <c r="B61" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>577143</v>
+        <v>577150</v>
       </c>
       <c r="R61" t="n">
-        <v>6711958</v>
+        <v>6711962</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7220,10 +7220,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125687144</v>
+        <v>125687128</v>
       </c>
       <c r="B62" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7264,10 +7264,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577150</v>
+        <v>577194</v>
       </c>
       <c r="R62" t="n">
-        <v>6711962</v>
+        <v>6711897</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7326,10 +7326,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125687128</v>
+        <v>125687141</v>
       </c>
       <c r="B63" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577194</v>
+        <v>577143</v>
       </c>
       <c r="R63" t="n">
-        <v>6711897</v>
+        <v>6711958</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7432,10 +7432,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125687110</v>
+        <v>125687113</v>
       </c>
       <c r="B64" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7470,23 +7470,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>577101</v>
+        <v>577142</v>
       </c>
       <c r="R64" t="n">
-        <v>6711989</v>
+        <v>6711971</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7527,7 +7520,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7546,10 +7538,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125687113</v>
+        <v>125687110</v>
       </c>
       <c r="B65" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7568,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7584,16 +7576,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>577142</v>
+        <v>577101</v>
       </c>
       <c r="R65" t="n">
-        <v>6711971</v>
+        <v>6711989</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7634,6 +7633,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7652,10 +7652,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125687112</v>
+        <v>125687134</v>
       </c>
       <c r="B66" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>577130</v>
+        <v>577126</v>
       </c>
       <c r="R66" t="n">
-        <v>6711953</v>
+        <v>6711880</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7758,10 +7758,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125687134</v>
+        <v>125687112</v>
       </c>
       <c r="B67" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7802,10 +7802,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>577126</v>
+        <v>577130</v>
       </c>
       <c r="R67" t="n">
-        <v>6711880</v>
+        <v>6711953</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7864,10 +7864,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125687124</v>
+        <v>125687137</v>
       </c>
       <c r="B68" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7908,10 +7908,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>577103</v>
+        <v>577195</v>
       </c>
       <c r="R68" t="n">
-        <v>6711980</v>
+        <v>6711896</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7970,10 +7970,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125687137</v>
+        <v>125687124</v>
       </c>
       <c r="B69" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>577195</v>
+        <v>577103</v>
       </c>
       <c r="R69" t="n">
-        <v>6711896</v>
+        <v>6711980</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8076,10 +8076,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125687126</v>
+        <v>125687129</v>
       </c>
       <c r="B70" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>577173</v>
+        <v>577096</v>
       </c>
       <c r="R70" t="n">
-        <v>6711932</v>
+        <v>6711969</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8182,10 +8182,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125687129</v>
+        <v>125687126</v>
       </c>
       <c r="B71" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8226,10 +8226,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>577096</v>
+        <v>577173</v>
       </c>
       <c r="R71" t="n">
-        <v>6711969</v>
+        <v>6711932</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8288,10 +8288,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125687119</v>
+        <v>125687120</v>
       </c>
       <c r="B72" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8326,16 +8326,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>577190</v>
+        <v>577187</v>
       </c>
       <c r="R72" t="n">
-        <v>6711913</v>
+        <v>6711920</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8376,6 +8383,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8397,7 +8405,7 @@
         <v>125687115</v>
       </c>
       <c r="B73" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8500,10 +8508,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125687120</v>
+        <v>125687119</v>
       </c>
       <c r="B74" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8530,7 +8538,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8538,23 +8546,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>577187</v>
+        <v>577190</v>
       </c>
       <c r="R74" t="n">
-        <v>6711920</v>
+        <v>6711913</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8595,7 +8596,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8614,32 +8614,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125687096</v>
+        <v>125687087</v>
       </c>
       <c r="B75" t="n">
-        <v>103769</v>
+        <v>96592</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>577145</v>
+        <v>577157</v>
       </c>
       <c r="R75" t="n">
-        <v>6711831</v>
+        <v>6711975</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8711,45 +8711,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125687148</v>
+        <v>125687125</v>
       </c>
       <c r="B76" t="n">
-        <v>98255</v>
+        <v>98339</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>577163</v>
+        <v>577172</v>
       </c>
       <c r="R76" t="n">
-        <v>6711969</v>
+        <v>6711942</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8808,54 +8817,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125687125</v>
+        <v>125687148</v>
       </c>
       <c r="B77" t="n">
-        <v>98338</v>
+        <v>98256</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>577172</v>
+        <v>577163</v>
       </c>
       <c r="R77" t="n">
-        <v>6711942</v>
+        <v>6711969</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8914,32 +8914,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125687087</v>
+        <v>125687096</v>
       </c>
       <c r="B78" t="n">
-        <v>96591</v>
+        <v>103770</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>222412</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8949,10 +8949,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>577157</v>
+        <v>577145</v>
       </c>
       <c r="R78" t="n">
-        <v>6711975</v>
+        <v>6711831</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9011,50 +9011,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125687097</v>
+        <v>125687088</v>
       </c>
       <c r="B79" t="n">
-        <v>4772</v>
+        <v>96592</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>577154</v>
+        <v>577173</v>
       </c>
       <c r="R79" t="n">
-        <v>6711917</v>
+        <v>6711943</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9113,42 +9108,38 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125687146</v>
+        <v>125687097</v>
       </c>
       <c r="B80" t="n">
-        <v>98338</v>
+        <v>4772</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9157,10 +9148,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>577165</v>
+        <v>577154</v>
       </c>
       <c r="R80" t="n">
-        <v>6711956</v>
+        <v>6711917</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9219,45 +9210,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125687088</v>
+        <v>125687146</v>
       </c>
       <c r="B81" t="n">
-        <v>96591</v>
+        <v>98339</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>577173</v>
+        <v>577165</v>
       </c>
       <c r="R81" t="n">
-        <v>6711943</v>
+        <v>6711956</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9413,10 +9413,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125687132</v>
+        <v>125687117</v>
       </c>
       <c r="B83" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>577153</v>
+        <v>577124</v>
       </c>
       <c r="R83" t="n">
         <v>6711978</v>
@@ -9519,10 +9519,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125687117</v>
+        <v>125687132</v>
       </c>
       <c r="B84" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>577124</v>
+        <v>577153</v>
       </c>
       <c r="R84" t="n">
         <v>6711978</v>
@@ -9625,10 +9625,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125687118</v>
+        <v>125687135</v>
       </c>
       <c r="B85" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -9669,10 +9669,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>577129</v>
+        <v>577117</v>
       </c>
       <c r="R85" t="n">
-        <v>6711973</v>
+        <v>6712004</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9731,10 +9731,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125687135</v>
+        <v>125687118</v>
       </c>
       <c r="B86" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -9775,10 +9775,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>577117</v>
+        <v>577129</v>
       </c>
       <c r="R86" t="n">
-        <v>6712004</v>
+        <v>6711973</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -4040,54 +4040,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125687116</v>
+        <v>125687079</v>
       </c>
       <c r="B31" t="n">
-        <v>98339</v>
+        <v>96592</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577202</v>
+        <v>577171</v>
       </c>
       <c r="R31" t="n">
-        <v>6711890</v>
+        <v>6711847</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4146,7 +4137,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125687142</v>
+        <v>125687116</v>
       </c>
       <c r="B32" t="n">
         <v>98339</v>
@@ -4176,7 +4167,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4190,10 +4181,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577150</v>
+        <v>577202</v>
       </c>
       <c r="R32" t="n">
-        <v>6711955</v>
+        <v>6711890</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4252,7 +4243,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125687123</v>
+        <v>125687142</v>
       </c>
       <c r="B33" t="n">
         <v>98339</v>
@@ -4282,7 +4273,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4296,10 +4287,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577090</v>
+        <v>577150</v>
       </c>
       <c r="R33" t="n">
-        <v>6711978</v>
+        <v>6711955</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4358,45 +4349,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125687079</v>
+        <v>125687123</v>
       </c>
       <c r="B34" t="n">
-        <v>96592</v>
+        <v>98339</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577171</v>
+        <v>577090</v>
       </c>
       <c r="R34" t="n">
-        <v>6711847</v>
+        <v>6711978</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4869,42 +4869,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125687130</v>
+        <v>125687150</v>
       </c>
       <c r="B39" t="n">
-        <v>98339</v>
+        <v>5176</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4913,10 +4909,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577105</v>
+        <v>577174</v>
       </c>
       <c r="R39" t="n">
-        <v>6711976</v>
+        <v>6711873</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4975,7 +4971,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125687122</v>
+        <v>125687130</v>
       </c>
       <c r="B40" t="n">
         <v>98339</v>
@@ -5005,7 +5001,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5019,10 +5015,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577145</v>
+        <v>577105</v>
       </c>
       <c r="R40" t="n">
-        <v>6711917</v>
+        <v>6711976</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5081,7 +5077,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125687140</v>
+        <v>125687122</v>
       </c>
       <c r="B41" t="n">
         <v>98339</v>
@@ -5111,7 +5107,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5125,10 +5121,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577141</v>
+        <v>577145</v>
       </c>
       <c r="R41" t="n">
-        <v>6711960</v>
+        <v>6711917</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5187,38 +5183,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125687150</v>
+        <v>125687140</v>
       </c>
       <c r="B42" t="n">
-        <v>5176</v>
+        <v>98339</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577174</v>
+        <v>577141</v>
       </c>
       <c r="R42" t="n">
-        <v>6711873</v>
+        <v>6711960</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5996,32 +5996,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125687152</v>
+        <v>125687082</v>
       </c>
       <c r="B50" t="n">
-        <v>102568</v>
+        <v>96592</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>223246</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577131</v>
+        <v>577110</v>
       </c>
       <c r="R50" t="n">
-        <v>6711836</v>
+        <v>6711911</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6069,18 +6069,12 @@
           <t>2025-06-04</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>12 cm dbh</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6099,45 +6093,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125687082</v>
+        <v>125687131</v>
       </c>
       <c r="B51" t="n">
-        <v>96592</v>
+        <v>98339</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577110</v>
+        <v>577148</v>
       </c>
       <c r="R51" t="n">
-        <v>6711911</v>
+        <v>6711976</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6196,54 +6199,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125687131</v>
+        <v>125687152</v>
       </c>
       <c r="B52" t="n">
-        <v>98339</v>
+        <v>102568</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>223246</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577148</v>
+        <v>577131</v>
       </c>
       <c r="R52" t="n">
-        <v>6711976</v>
+        <v>6711836</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6278,12 +6272,18 @@
           <t>2025-06-04</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>12 cm dbh</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -5289,54 +5289,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125687145</v>
+        <v>125687093</v>
       </c>
       <c r="B43" t="n">
-        <v>98339</v>
+        <v>91232</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577155</v>
+        <v>577243</v>
       </c>
       <c r="R43" t="n">
-        <v>6711978</v>
+        <v>6711783</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5395,32 +5386,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125687090</v>
+        <v>125687091</v>
       </c>
       <c r="B44" t="n">
-        <v>91197</v>
+        <v>91232</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5430,10 +5421,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577215</v>
+        <v>577156</v>
       </c>
       <c r="R44" t="n">
-        <v>6711829</v>
+        <v>6711864</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5492,32 +5483,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125687093</v>
+        <v>125687090</v>
       </c>
       <c r="B45" t="n">
-        <v>91232</v>
+        <v>91197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5527,10 +5518,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577243</v>
+        <v>577215</v>
       </c>
       <c r="R45" t="n">
-        <v>6711783</v>
+        <v>6711829</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5589,45 +5580,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125687091</v>
+        <v>125687151</v>
       </c>
       <c r="B46" t="n">
-        <v>91232</v>
+        <v>5176</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577156</v>
+        <v>577176</v>
       </c>
       <c r="R46" t="n">
-        <v>6711864</v>
+        <v>6711840</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5686,38 +5682,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125687151</v>
+        <v>125687145</v>
       </c>
       <c r="B47" t="n">
-        <v>5176</v>
+        <v>98339</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5726,10 +5726,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577176</v>
+        <v>577155</v>
       </c>
       <c r="R47" t="n">
-        <v>6711840</v>
+        <v>6711978</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5996,32 +5996,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125687082</v>
+        <v>125687152</v>
       </c>
       <c r="B50" t="n">
-        <v>96592</v>
+        <v>102568</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>223246</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577110</v>
+        <v>577131</v>
       </c>
       <c r="R50" t="n">
-        <v>6711911</v>
+        <v>6711836</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6069,12 +6069,18 @@
           <t>2025-06-04</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>12 cm dbh</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6093,54 +6099,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125687131</v>
+        <v>125687082</v>
       </c>
       <c r="B51" t="n">
-        <v>98339</v>
+        <v>96592</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577148</v>
+        <v>577110</v>
       </c>
       <c r="R51" t="n">
-        <v>6711976</v>
+        <v>6711911</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6199,45 +6196,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125687152</v>
+        <v>125687131</v>
       </c>
       <c r="B52" t="n">
-        <v>102568</v>
+        <v>98339</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>223246</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577131</v>
+        <v>577148</v>
       </c>
       <c r="R52" t="n">
-        <v>6711836</v>
+        <v>6711976</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6272,18 +6278,12 @@
           <t>2025-06-04</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>12 cm dbh</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -3622,7 +3622,7 @@
         <v>125512020</v>
       </c>
       <c r="B27" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3740,54 +3740,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125687111</v>
+        <v>125687083</v>
       </c>
       <c r="B28" t="n">
-        <v>98339</v>
+        <v>96594</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577182</v>
+        <v>577154</v>
       </c>
       <c r="R28" t="n">
-        <v>6711920</v>
+        <v>6711905</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3846,10 +3837,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125687083</v>
+        <v>125687078</v>
       </c>
       <c r="B29" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3881,10 +3872,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577154</v>
+        <v>577169</v>
       </c>
       <c r="R29" t="n">
-        <v>6711905</v>
+        <v>6711894</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3943,45 +3934,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125687078</v>
+        <v>125687111</v>
       </c>
       <c r="B30" t="n">
-        <v>96592</v>
+        <v>98341</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577169</v>
+        <v>577182</v>
       </c>
       <c r="R30" t="n">
-        <v>6711894</v>
+        <v>6711920</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4040,45 +4040,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125687079</v>
+        <v>125687116</v>
       </c>
       <c r="B31" t="n">
-        <v>96592</v>
+        <v>98341</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577171</v>
+        <v>577202</v>
       </c>
       <c r="R31" t="n">
-        <v>6711847</v>
+        <v>6711890</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4137,10 +4146,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125687116</v>
+        <v>125687142</v>
       </c>
       <c r="B32" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4167,7 +4176,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4181,10 +4190,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577202</v>
+        <v>577150</v>
       </c>
       <c r="R32" t="n">
-        <v>6711890</v>
+        <v>6711955</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4243,10 +4252,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125687142</v>
+        <v>125687123</v>
       </c>
       <c r="B33" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4273,7 +4282,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4287,10 +4296,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577150</v>
+        <v>577090</v>
       </c>
       <c r="R33" t="n">
-        <v>6711955</v>
+        <v>6711978</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4349,54 +4358,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125687123</v>
+        <v>125687079</v>
       </c>
       <c r="B34" t="n">
-        <v>98339</v>
+        <v>96594</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577090</v>
+        <v>577171</v>
       </c>
       <c r="R34" t="n">
-        <v>6711978</v>
+        <v>6711847</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
         <v>125687086</v>
       </c>
       <c r="B35" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>125687121</v>
       </c>
       <c r="B36" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>125687127</v>
       </c>
       <c r="B37" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4772,45 +4772,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125687092</v>
+        <v>125687150</v>
       </c>
       <c r="B38" t="n">
-        <v>91232</v>
+        <v>5176</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577169</v>
+        <v>577174</v>
       </c>
       <c r="R38" t="n">
-        <v>6711859</v>
+        <v>6711873</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4869,50 +4874,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125687150</v>
+        <v>125687092</v>
       </c>
       <c r="B39" t="n">
-        <v>5176</v>
+        <v>91234</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577174</v>
+        <v>577169</v>
       </c>
       <c r="R39" t="n">
-        <v>6711873</v>
+        <v>6711859</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4974,7 +4974,7 @@
         <v>125687130</v>
       </c>
       <c r="B40" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>125687122</v>
       </c>
       <c r="B41" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>125687140</v>
       </c>
       <c r="B42" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>125687093</v>
       </c>
       <c r="B43" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>125687091</v>
       </c>
       <c r="B44" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>125687090</v>
       </c>
       <c r="B45" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>125687145</v>
       </c>
       <c r="B47" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5788,54 +5788,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125687133</v>
+        <v>125687081</v>
       </c>
       <c r="B48" t="n">
-        <v>98339</v>
+        <v>96594</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577171</v>
+        <v>577109</v>
       </c>
       <c r="R48" t="n">
-        <v>6711869</v>
+        <v>6711890</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5868,11 +5859,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5899,45 +5885,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125687081</v>
+        <v>125687133</v>
       </c>
       <c r="B49" t="n">
-        <v>96592</v>
+        <v>98341</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577109</v>
+        <v>577171</v>
       </c>
       <c r="R49" t="n">
-        <v>6711890</v>
+        <v>6711869</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5970,6 +5965,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5996,45 +5996,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125687152</v>
+        <v>125687131</v>
       </c>
       <c r="B50" t="n">
-        <v>102568</v>
+        <v>98341</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>223246</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577131</v>
+        <v>577148</v>
       </c>
       <c r="R50" t="n">
-        <v>6711836</v>
+        <v>6711976</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6069,18 +6078,12 @@
           <t>2025-06-04</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>12 cm dbh</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6099,32 +6102,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125687082</v>
+        <v>125687152</v>
       </c>
       <c r="B51" t="n">
-        <v>96592</v>
+        <v>102570</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>223246</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6134,10 +6137,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577110</v>
+        <v>577131</v>
       </c>
       <c r="R51" t="n">
-        <v>6711911</v>
+        <v>6711836</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6172,12 +6175,18 @@
           <t>2025-06-04</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>12 cm dbh</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6196,54 +6205,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125687131</v>
+        <v>125687082</v>
       </c>
       <c r="B52" t="n">
-        <v>98339</v>
+        <v>96594</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577148</v>
+        <v>577110</v>
       </c>
       <c r="R52" t="n">
-        <v>6711976</v>
+        <v>6711911</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6305,7 +6305,7 @@
         <v>125687149</v>
       </c>
       <c r="B53" t="n">
-        <v>95191</v>
+        <v>95193</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>125687084</v>
       </c>
       <c r="B54" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>125687139</v>
       </c>
       <c r="B55" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>125687136</v>
       </c>
       <c r="B56" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>125687095</v>
       </c>
       <c r="B57" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>125687143</v>
       </c>
       <c r="B58" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>125687085</v>
       </c>
       <c r="B59" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>125687114</v>
       </c>
       <c r="B60" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>125687144</v>
       </c>
       <c r="B61" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>125687128</v>
       </c>
       <c r="B62" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>125687141</v>
       </c>
       <c r="B63" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>125687113</v>
       </c>
       <c r="B64" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>125687110</v>
       </c>
       <c r="B65" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>125687134</v>
       </c>
       <c r="B66" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>125687112</v>
       </c>
       <c r="B67" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>125687137</v>
       </c>
       <c r="B68" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>125687124</v>
       </c>
       <c r="B69" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>125687129</v>
       </c>
       <c r="B70" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>125687126</v>
       </c>
       <c r="B71" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>125687120</v>
       </c>
       <c r="B72" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>125687115</v>
       </c>
       <c r="B73" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>125687119</v>
       </c>
       <c r="B74" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>125687087</v>
       </c>
       <c r="B75" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>125687125</v>
       </c>
       <c r="B76" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>125687148</v>
       </c>
       <c r="B77" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>125687096</v>
       </c>
       <c r="B78" t="n">
-        <v>103770</v>
+        <v>103772</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>125687088</v>
       </c>
       <c r="B79" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>125687146</v>
       </c>
       <c r="B81" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>125687094</v>
       </c>
       <c r="B82" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>125687117</v>
       </c>
       <c r="B83" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>125687132</v>
       </c>
       <c r="B84" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>125687135</v>
       </c>
       <c r="B85" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>125687118</v>
       </c>
       <c r="B86" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -4874,45 +4874,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125687092</v>
+        <v>125687130</v>
       </c>
       <c r="B39" t="n">
-        <v>91234</v>
+        <v>98341</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577169</v>
+        <v>577105</v>
       </c>
       <c r="R39" t="n">
-        <v>6711859</v>
+        <v>6711976</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4971,7 +4980,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125687130</v>
+        <v>125687122</v>
       </c>
       <c r="B40" t="n">
         <v>98341</v>
@@ -5001,7 +5010,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5015,10 +5024,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577105</v>
+        <v>577145</v>
       </c>
       <c r="R40" t="n">
-        <v>6711976</v>
+        <v>6711917</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5077,7 +5086,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125687122</v>
+        <v>125687140</v>
       </c>
       <c r="B41" t="n">
         <v>98341</v>
@@ -5107,7 +5116,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5121,10 +5130,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577145</v>
+        <v>577141</v>
       </c>
       <c r="R41" t="n">
-        <v>6711917</v>
+        <v>6711960</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5183,54 +5192,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125687140</v>
+        <v>125687092</v>
       </c>
       <c r="B42" t="n">
-        <v>98341</v>
+        <v>91234</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577141</v>
+        <v>577169</v>
       </c>
       <c r="R42" t="n">
-        <v>6711960</v>
+        <v>6711859</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6911,45 +6911,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125687085</v>
+        <v>125687114</v>
       </c>
       <c r="B59" t="n">
-        <v>96594</v>
+        <v>98341</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>577130</v>
+        <v>577145</v>
       </c>
       <c r="R59" t="n">
-        <v>6711985</v>
+        <v>6711974</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7008,54 +7017,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125687114</v>
+        <v>125687085</v>
       </c>
       <c r="B60" t="n">
-        <v>98341</v>
+        <v>96594</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577145</v>
+        <v>577130</v>
       </c>
       <c r="R60" t="n">
-        <v>6711974</v>
+        <v>6711985</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8817,10 +8817,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125687148</v>
+        <v>125687096</v>
       </c>
       <c r="B77" t="n">
-        <v>98258</v>
+        <v>103772</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8828,21 +8828,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219790</v>
+        <v>222412</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>577163</v>
+        <v>577145</v>
       </c>
       <c r="R77" t="n">
-        <v>6711969</v>
+        <v>6711831</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8914,10 +8914,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125687096</v>
+        <v>125687148</v>
       </c>
       <c r="B78" t="n">
-        <v>103772</v>
+        <v>98258</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8925,21 +8925,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222412</v>
+        <v>219790</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8949,10 +8949,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>577145</v>
+        <v>577163</v>
       </c>
       <c r="R78" t="n">
-        <v>6711831</v>
+        <v>6711969</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -3622,7 +3622,7 @@
         <v>125512020</v>
       </c>
       <c r="B27" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>125687083</v>
       </c>
       <c r="B28" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>125687078</v>
       </c>
       <c r="B29" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>125687111</v>
       </c>
       <c r="B30" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4040,54 +4040,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125687116</v>
+        <v>125687079</v>
       </c>
       <c r="B31" t="n">
-        <v>98341</v>
+        <v>96596</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577202</v>
+        <v>577171</v>
       </c>
       <c r="R31" t="n">
-        <v>6711890</v>
+        <v>6711847</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4149,7 +4140,7 @@
         <v>125687142</v>
       </c>
       <c r="B32" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4255,7 +4246,7 @@
         <v>125687123</v>
       </c>
       <c r="B33" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4358,45 +4349,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125687079</v>
+        <v>125687116</v>
       </c>
       <c r="B34" t="n">
-        <v>96594</v>
+        <v>98343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577171</v>
+        <v>577202</v>
       </c>
       <c r="R34" t="n">
-        <v>6711847</v>
+        <v>6711890</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
         <v>125687086</v>
       </c>
       <c r="B35" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>125687121</v>
       </c>
       <c r="B36" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>125687127</v>
       </c>
       <c r="B37" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4772,50 +4772,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125687150</v>
+        <v>125687092</v>
       </c>
       <c r="B38" t="n">
-        <v>5176</v>
+        <v>91236</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577174</v>
+        <v>577169</v>
       </c>
       <c r="R38" t="n">
-        <v>6711873</v>
+        <v>6711859</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4874,10 +4869,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125687130</v>
+        <v>125687122</v>
       </c>
       <c r="B39" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4904,7 +4899,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4918,10 +4913,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577105</v>
+        <v>577145</v>
       </c>
       <c r="R39" t="n">
-        <v>6711976</v>
+        <v>6711917</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4980,10 +4975,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125687122</v>
+        <v>125687130</v>
       </c>
       <c r="B40" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5010,7 +5005,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5024,10 +5019,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577145</v>
+        <v>577105</v>
       </c>
       <c r="R40" t="n">
-        <v>6711917</v>
+        <v>6711976</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5089,7 +5084,7 @@
         <v>125687140</v>
       </c>
       <c r="B41" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5192,45 +5187,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125687092</v>
+        <v>125687150</v>
       </c>
       <c r="B42" t="n">
-        <v>91234</v>
+        <v>5176</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577169</v>
+        <v>577174</v>
       </c>
       <c r="R42" t="n">
-        <v>6711859</v>
+        <v>6711873</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5289,45 +5289,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125687093</v>
+        <v>125687151</v>
       </c>
       <c r="B43" t="n">
-        <v>91234</v>
+        <v>5176</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577243</v>
+        <v>577176</v>
       </c>
       <c r="R43" t="n">
-        <v>6711783</v>
+        <v>6711840</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5386,45 +5391,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125687091</v>
+        <v>125687145</v>
       </c>
       <c r="B44" t="n">
-        <v>91234</v>
+        <v>98343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577156</v>
+        <v>577155</v>
       </c>
       <c r="R44" t="n">
-        <v>6711864</v>
+        <v>6711978</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5486,7 +5500,7 @@
         <v>125687090</v>
       </c>
       <c r="B45" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5580,50 +5594,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125687151</v>
+        <v>125687093</v>
       </c>
       <c r="B46" t="n">
-        <v>5176</v>
+        <v>91236</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577176</v>
+        <v>577243</v>
       </c>
       <c r="R46" t="n">
-        <v>6711840</v>
+        <v>6711783</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5682,54 +5691,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125687145</v>
+        <v>125687091</v>
       </c>
       <c r="B47" t="n">
-        <v>98341</v>
+        <v>91236</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577155</v>
+        <v>577156</v>
       </c>
       <c r="R47" t="n">
-        <v>6711978</v>
+        <v>6711864</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5788,45 +5788,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125687081</v>
+        <v>125687133</v>
       </c>
       <c r="B48" t="n">
-        <v>96594</v>
+        <v>98343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577109</v>
+        <v>577171</v>
       </c>
       <c r="R48" t="n">
-        <v>6711890</v>
+        <v>6711869</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5859,6 +5868,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5885,54 +5899,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125687133</v>
+        <v>125687081</v>
       </c>
       <c r="B49" t="n">
-        <v>98341</v>
+        <v>96596</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577171</v>
+        <v>577109</v>
       </c>
       <c r="R49" t="n">
-        <v>6711869</v>
+        <v>6711890</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5965,11 +5970,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5999,7 +5999,7 @@
         <v>125687131</v>
       </c>
       <c r="B50" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6102,32 +6102,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125687152</v>
+        <v>125687082</v>
       </c>
       <c r="B51" t="n">
-        <v>102570</v>
+        <v>96596</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>223246</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577131</v>
+        <v>577110</v>
       </c>
       <c r="R51" t="n">
-        <v>6711836</v>
+        <v>6711911</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6175,18 +6175,12 @@
           <t>2025-06-04</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>12 cm dbh</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6205,32 +6199,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125687082</v>
+        <v>125687152</v>
       </c>
       <c r="B52" t="n">
-        <v>96594</v>
+        <v>102572</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>223246</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6240,10 +6234,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577110</v>
+        <v>577131</v>
       </c>
       <c r="R52" t="n">
-        <v>6711911</v>
+        <v>6711836</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6278,12 +6272,18 @@
           <t>2025-06-04</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>12 cm dbh</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6305,7 +6305,7 @@
         <v>125687149</v>
       </c>
       <c r="B53" t="n">
-        <v>95193</v>
+        <v>95195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6399,45 +6399,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125687084</v>
+        <v>125687136</v>
       </c>
       <c r="B54" t="n">
-        <v>96594</v>
+        <v>98343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577088</v>
+        <v>577187</v>
       </c>
       <c r="R54" t="n">
-        <v>6711963</v>
+        <v>6711916</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6499,7 +6508,7 @@
         <v>125687139</v>
       </c>
       <c r="B55" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,54 +6611,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125687136</v>
+        <v>125687084</v>
       </c>
       <c r="B56" t="n">
-        <v>98341</v>
+        <v>96596</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>577187</v>
+        <v>577088</v>
       </c>
       <c r="R56" t="n">
-        <v>6711916</v>
+        <v>6711963</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6711,7 +6711,7 @@
         <v>125687095</v>
       </c>
       <c r="B57" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>125687143</v>
       </c>
       <c r="B58" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>125687114</v>
       </c>
       <c r="B59" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>125687085</v>
       </c>
       <c r="B60" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7114,10 +7114,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125687144</v>
+        <v>125687141</v>
       </c>
       <c r="B61" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>577150</v>
+        <v>577143</v>
       </c>
       <c r="R61" t="n">
-        <v>6711962</v>
+        <v>6711958</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7220,10 +7220,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125687128</v>
+        <v>125687144</v>
       </c>
       <c r="B62" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7264,10 +7264,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577194</v>
+        <v>577150</v>
       </c>
       <c r="R62" t="n">
-        <v>6711897</v>
+        <v>6711962</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7326,10 +7326,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125687141</v>
+        <v>125687128</v>
       </c>
       <c r="B63" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577143</v>
+        <v>577194</v>
       </c>
       <c r="R63" t="n">
-        <v>6711958</v>
+        <v>6711897</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7432,10 +7432,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125687113</v>
+        <v>125687110</v>
       </c>
       <c r="B64" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7470,16 +7470,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>577142</v>
+        <v>577101</v>
       </c>
       <c r="R64" t="n">
-        <v>6711971</v>
+        <v>6711989</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7520,6 +7527,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7538,10 +7546,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125687110</v>
+        <v>125687113</v>
       </c>
       <c r="B65" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7568,7 +7576,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7576,23 +7584,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>577101</v>
+        <v>577142</v>
       </c>
       <c r="R65" t="n">
-        <v>6711989</v>
+        <v>6711971</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7633,7 +7634,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7652,10 +7652,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125687134</v>
+        <v>125687112</v>
       </c>
       <c r="B66" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>577126</v>
+        <v>577130</v>
       </c>
       <c r="R66" t="n">
-        <v>6711880</v>
+        <v>6711953</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7758,10 +7758,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125687112</v>
+        <v>125687134</v>
       </c>
       <c r="B67" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7802,10 +7802,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>577130</v>
+        <v>577126</v>
       </c>
       <c r="R67" t="n">
-        <v>6711953</v>
+        <v>6711880</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7864,10 +7864,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125687137</v>
+        <v>125687124</v>
       </c>
       <c r="B68" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7908,10 +7908,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>577195</v>
+        <v>577103</v>
       </c>
       <c r="R68" t="n">
-        <v>6711896</v>
+        <v>6711980</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7970,10 +7970,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125687124</v>
+        <v>125687137</v>
       </c>
       <c r="B69" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>577103</v>
+        <v>577195</v>
       </c>
       <c r="R69" t="n">
-        <v>6711980</v>
+        <v>6711896</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8076,10 +8076,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125687129</v>
+        <v>125687126</v>
       </c>
       <c r="B70" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>577096</v>
+        <v>577173</v>
       </c>
       <c r="R70" t="n">
-        <v>6711969</v>
+        <v>6711932</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8182,10 +8182,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125687126</v>
+        <v>125687129</v>
       </c>
       <c r="B71" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8226,10 +8226,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>577173</v>
+        <v>577096</v>
       </c>
       <c r="R71" t="n">
-        <v>6711932</v>
+        <v>6711969</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8288,10 +8288,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125687120</v>
+        <v>125687119</v>
       </c>
       <c r="B72" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8326,23 +8326,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>577187</v>
+        <v>577190</v>
       </c>
       <c r="R72" t="n">
-        <v>6711920</v>
+        <v>6711913</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8383,7 +8376,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8405,7 +8397,7 @@
         <v>125687115</v>
       </c>
       <c r="B73" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8508,10 +8500,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125687119</v>
+        <v>125687120</v>
       </c>
       <c r="B74" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8538,7 +8530,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8546,16 +8538,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>577190</v>
+        <v>577187</v>
       </c>
       <c r="R74" t="n">
-        <v>6711913</v>
+        <v>6711920</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8596,6 +8595,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8617,7 +8617,7 @@
         <v>125687087</v>
       </c>
       <c r="B75" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>125687125</v>
       </c>
       <c r="B76" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8817,10 +8817,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125687096</v>
+        <v>125687148</v>
       </c>
       <c r="B77" t="n">
-        <v>103772</v>
+        <v>98260</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8828,21 +8828,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222412</v>
+        <v>219790</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>577145</v>
+        <v>577163</v>
       </c>
       <c r="R77" t="n">
-        <v>6711831</v>
+        <v>6711969</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8914,10 +8914,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125687148</v>
+        <v>125687096</v>
       </c>
       <c r="B78" t="n">
-        <v>98258</v>
+        <v>103774</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8925,21 +8925,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219790</v>
+        <v>222412</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8949,10 +8949,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>577163</v>
+        <v>577145</v>
       </c>
       <c r="R78" t="n">
-        <v>6711969</v>
+        <v>6711831</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9014,7 +9014,7 @@
         <v>125687088</v>
       </c>
       <c r="B79" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>125687146</v>
       </c>
       <c r="B81" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>125687094</v>
       </c>
       <c r="B82" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9413,10 +9413,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125687117</v>
+        <v>125687132</v>
       </c>
       <c r="B83" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>577124</v>
+        <v>577153</v>
       </c>
       <c r="R83" t="n">
         <v>6711978</v>
@@ -9519,10 +9519,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125687132</v>
+        <v>125687117</v>
       </c>
       <c r="B84" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>577153</v>
+        <v>577124</v>
       </c>
       <c r="R84" t="n">
         <v>6711978</v>
@@ -9625,10 +9625,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125687135</v>
+        <v>125687118</v>
       </c>
       <c r="B85" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -9669,10 +9669,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>577117</v>
+        <v>577129</v>
       </c>
       <c r="R85" t="n">
-        <v>6712004</v>
+        <v>6711973</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9731,10 +9731,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125687118</v>
+        <v>125687135</v>
       </c>
       <c r="B86" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -9775,10 +9775,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>577129</v>
+        <v>577117</v>
       </c>
       <c r="R86" t="n">
-        <v>6711973</v>
+        <v>6712004</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -4772,45 +4772,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125687092</v>
+        <v>125687150</v>
       </c>
       <c r="B38" t="n">
-        <v>91236</v>
+        <v>5176</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577169</v>
+        <v>577174</v>
       </c>
       <c r="R38" t="n">
-        <v>6711859</v>
+        <v>6711873</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4869,54 +4874,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125687122</v>
+        <v>125687092</v>
       </c>
       <c r="B39" t="n">
-        <v>98343</v>
+        <v>91236</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577145</v>
+        <v>577169</v>
       </c>
       <c r="R39" t="n">
-        <v>6711917</v>
+        <v>6711859</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4975,7 +4971,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125687130</v>
+        <v>125687122</v>
       </c>
       <c r="B40" t="n">
         <v>98343</v>
@@ -5005,7 +5001,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5019,10 +5015,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577105</v>
+        <v>577145</v>
       </c>
       <c r="R40" t="n">
-        <v>6711976</v>
+        <v>6711917</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5081,7 +5077,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125687140</v>
+        <v>125687130</v>
       </c>
       <c r="B41" t="n">
         <v>98343</v>
@@ -5111,7 +5107,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5125,10 +5121,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577141</v>
+        <v>577105</v>
       </c>
       <c r="R41" t="n">
-        <v>6711960</v>
+        <v>6711976</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5187,38 +5183,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125687150</v>
+        <v>125687140</v>
       </c>
       <c r="B42" t="n">
-        <v>5176</v>
+        <v>98343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577174</v>
+        <v>577141</v>
       </c>
       <c r="R42" t="n">
-        <v>6711873</v>
+        <v>6711960</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125687151</v>
+        <v>125687090</v>
       </c>
       <c r="B43" t="n">
-        <v>5176</v>
+        <v>91201</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5300,39 +5300,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577176</v>
+        <v>577215</v>
       </c>
       <c r="R43" t="n">
-        <v>6711840</v>
+        <v>6711829</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5391,42 +5386,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125687145</v>
+        <v>125687151</v>
       </c>
       <c r="B44" t="n">
-        <v>98343</v>
+        <v>5176</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5435,10 +5426,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577155</v>
+        <v>577176</v>
       </c>
       <c r="R44" t="n">
-        <v>6711978</v>
+        <v>6711840</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5497,32 +5488,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125687090</v>
+        <v>125687093</v>
       </c>
       <c r="B45" t="n">
-        <v>91201</v>
+        <v>91236</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5532,10 +5523,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577215</v>
+        <v>577243</v>
       </c>
       <c r="R45" t="n">
-        <v>6711829</v>
+        <v>6711783</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5594,7 +5585,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125687093</v>
+        <v>125687091</v>
       </c>
       <c r="B46" t="n">
         <v>91236</v>
@@ -5629,10 +5620,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577243</v>
+        <v>577156</v>
       </c>
       <c r="R46" t="n">
-        <v>6711783</v>
+        <v>6711864</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5691,45 +5682,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125687091</v>
+        <v>125687145</v>
       </c>
       <c r="B47" t="n">
-        <v>91236</v>
+        <v>98343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577156</v>
+        <v>577155</v>
       </c>
       <c r="R47" t="n">
-        <v>6711864</v>
+        <v>6711978</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6399,54 +6399,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125687136</v>
+        <v>125687084</v>
       </c>
       <c r="B54" t="n">
-        <v>98343</v>
+        <v>96596</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577187</v>
+        <v>577088</v>
       </c>
       <c r="R54" t="n">
-        <v>6711916</v>
+        <v>6711963</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6505,7 +6496,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125687139</v>
+        <v>125687136</v>
       </c>
       <c r="B55" t="n">
         <v>98343</v>
@@ -6535,7 +6526,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6549,10 +6540,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>577090</v>
+        <v>577187</v>
       </c>
       <c r="R55" t="n">
-        <v>6711973</v>
+        <v>6711916</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6611,45 +6602,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125687084</v>
+        <v>125687139</v>
       </c>
       <c r="B56" t="n">
-        <v>96596</v>
+        <v>98343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>577088</v>
+        <v>577090</v>
       </c>
       <c r="R56" t="n">
-        <v>6711963</v>
+        <v>6711973</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6708,45 +6708,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125687095</v>
+        <v>125687143</v>
       </c>
       <c r="B57" t="n">
-        <v>91236</v>
+        <v>98343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>577135</v>
+        <v>577152</v>
       </c>
       <c r="R57" t="n">
-        <v>6711824</v>
+        <v>6711960</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6805,54 +6814,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125687143</v>
+        <v>125687095</v>
       </c>
       <c r="B58" t="n">
-        <v>98343</v>
+        <v>91236</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>577152</v>
+        <v>577135</v>
       </c>
       <c r="R58" t="n">
-        <v>6711960</v>
+        <v>6711824</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -3743,7 +3743,7 @@
         <v>125687083</v>
       </c>
       <c r="B28" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>125687078</v>
       </c>
       <c r="B29" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>125687111</v>
       </c>
       <c r="B30" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4040,45 +4040,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125687079</v>
+        <v>125687123</v>
       </c>
       <c r="B31" t="n">
-        <v>96596</v>
+        <v>98345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577171</v>
+        <v>577090</v>
       </c>
       <c r="R31" t="n">
-        <v>6711847</v>
+        <v>6711978</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4137,10 +4146,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125687142</v>
+        <v>125687116</v>
       </c>
       <c r="B32" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4167,7 +4176,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4181,10 +4190,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577150</v>
+        <v>577202</v>
       </c>
       <c r="R32" t="n">
-        <v>6711955</v>
+        <v>6711890</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4243,10 +4252,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125687123</v>
+        <v>125687142</v>
       </c>
       <c r="B33" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4273,7 +4282,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4287,10 +4296,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577090</v>
+        <v>577150</v>
       </c>
       <c r="R33" t="n">
-        <v>6711978</v>
+        <v>6711955</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4349,54 +4358,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125687116</v>
+        <v>125687079</v>
       </c>
       <c r="B34" t="n">
-        <v>98343</v>
+        <v>96598</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577202</v>
+        <v>577171</v>
       </c>
       <c r="R34" t="n">
-        <v>6711890</v>
+        <v>6711847</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
         <v>125687086</v>
       </c>
       <c r="B35" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>125687121</v>
       </c>
       <c r="B36" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>125687127</v>
       </c>
       <c r="B37" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>125687092</v>
       </c>
       <c r="B39" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>125687122</v>
       </c>
       <c r="B40" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>125687130</v>
       </c>
       <c r="B41" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>125687140</v>
       </c>
       <c r="B42" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5289,32 +5289,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125687090</v>
+        <v>125687093</v>
       </c>
       <c r="B43" t="n">
-        <v>91201</v>
+        <v>91238</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577215</v>
+        <v>577243</v>
       </c>
       <c r="R43" t="n">
-        <v>6711829</v>
+        <v>6711783</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5386,50 +5386,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125687151</v>
+        <v>125687091</v>
       </c>
       <c r="B44" t="n">
-        <v>5176</v>
+        <v>91238</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577176</v>
+        <v>577156</v>
       </c>
       <c r="R44" t="n">
-        <v>6711840</v>
+        <v>6711864</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5488,45 +5483,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125687093</v>
+        <v>125687151</v>
       </c>
       <c r="B45" t="n">
-        <v>91236</v>
+        <v>5176</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577243</v>
+        <v>577176</v>
       </c>
       <c r="R45" t="n">
-        <v>6711783</v>
+        <v>6711840</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5585,32 +5585,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125687091</v>
+        <v>125687090</v>
       </c>
       <c r="B46" t="n">
-        <v>91236</v>
+        <v>91203</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577156</v>
+        <v>577215</v>
       </c>
       <c r="R46" t="n">
-        <v>6711864</v>
+        <v>6711829</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5685,7 +5685,7 @@
         <v>125687145</v>
       </c>
       <c r="B47" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5788,54 +5788,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125687133</v>
+        <v>125687081</v>
       </c>
       <c r="B48" t="n">
-        <v>98343</v>
+        <v>96598</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577171</v>
+        <v>577109</v>
       </c>
       <c r="R48" t="n">
-        <v>6711869</v>
+        <v>6711890</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5868,11 +5859,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5899,45 +5885,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125687081</v>
+        <v>125687133</v>
       </c>
       <c r="B49" t="n">
-        <v>96596</v>
+        <v>98345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577109</v>
+        <v>577171</v>
       </c>
       <c r="R49" t="n">
-        <v>6711890</v>
+        <v>6711869</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5970,6 +5965,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5996,54 +5996,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125687131</v>
+        <v>125687082</v>
       </c>
       <c r="B50" t="n">
-        <v>98343</v>
+        <v>96598</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577148</v>
+        <v>577110</v>
       </c>
       <c r="R50" t="n">
-        <v>6711976</v>
+        <v>6711911</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6102,45 +6093,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125687082</v>
+        <v>125687131</v>
       </c>
       <c r="B51" t="n">
-        <v>96596</v>
+        <v>98345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577110</v>
+        <v>577148</v>
       </c>
       <c r="R51" t="n">
-        <v>6711911</v>
+        <v>6711976</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6202,7 +6202,7 @@
         <v>125687152</v>
       </c>
       <c r="B52" t="n">
-        <v>102572</v>
+        <v>102574</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>125687149</v>
       </c>
       <c r="B53" t="n">
-        <v>95195</v>
+        <v>95197</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>125687084</v>
       </c>
       <c r="B54" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6496,10 +6496,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125687136</v>
+        <v>125687139</v>
       </c>
       <c r="B55" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6540,10 +6540,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>577187</v>
+        <v>577090</v>
       </c>
       <c r="R55" t="n">
-        <v>6711916</v>
+        <v>6711973</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6602,10 +6602,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125687139</v>
+        <v>125687136</v>
       </c>
       <c r="B56" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>577090</v>
+        <v>577187</v>
       </c>
       <c r="R56" t="n">
-        <v>6711973</v>
+        <v>6711916</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6708,54 +6708,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125687143</v>
+        <v>125687095</v>
       </c>
       <c r="B57" t="n">
-        <v>98343</v>
+        <v>91238</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>577152</v>
+        <v>577135</v>
       </c>
       <c r="R57" t="n">
-        <v>6711960</v>
+        <v>6711824</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6814,45 +6805,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125687095</v>
+        <v>125687143</v>
       </c>
       <c r="B58" t="n">
-        <v>91236</v>
+        <v>98345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>577135</v>
+        <v>577152</v>
       </c>
       <c r="R58" t="n">
-        <v>6711824</v>
+        <v>6711960</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6911,54 +6911,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125687114</v>
+        <v>125687085</v>
       </c>
       <c r="B59" t="n">
-        <v>98343</v>
+        <v>96598</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>577145</v>
+        <v>577130</v>
       </c>
       <c r="R59" t="n">
-        <v>6711974</v>
+        <v>6711985</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7017,45 +7008,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125687085</v>
+        <v>125687114</v>
       </c>
       <c r="B60" t="n">
-        <v>96596</v>
+        <v>98345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577130</v>
+        <v>577145</v>
       </c>
       <c r="R60" t="n">
-        <v>6711985</v>
+        <v>6711974</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7117,7 +7117,7 @@
         <v>125687141</v>
       </c>
       <c r="B61" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>125687144</v>
       </c>
       <c r="B62" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7326,10 +7326,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125687128</v>
+        <v>125687110</v>
       </c>
       <c r="B63" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7364,16 +7364,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577194</v>
+        <v>577101</v>
       </c>
       <c r="R63" t="n">
-        <v>6711897</v>
+        <v>6711989</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7414,6 +7421,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7432,10 +7440,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125687110</v>
+        <v>125687128</v>
       </c>
       <c r="B64" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7462,7 +7470,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7470,23 +7478,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>577101</v>
+        <v>577194</v>
       </c>
       <c r="R64" t="n">
-        <v>6711989</v>
+        <v>6711897</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7527,7 +7528,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7549,7 +7549,7 @@
         <v>125687113</v>
       </c>
       <c r="B65" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>125687112</v>
       </c>
       <c r="B66" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>125687134</v>
       </c>
       <c r="B67" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>125687124</v>
       </c>
       <c r="B68" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>125687137</v>
       </c>
       <c r="B69" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8076,10 +8076,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125687126</v>
+        <v>125687120</v>
       </c>
       <c r="B70" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8114,16 +8114,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>577173</v>
+        <v>577187</v>
       </c>
       <c r="R70" t="n">
-        <v>6711932</v>
+        <v>6711920</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8164,6 +8171,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8182,10 +8190,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125687129</v>
+        <v>125687126</v>
       </c>
       <c r="B71" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8212,7 +8220,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8226,10 +8234,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>577096</v>
+        <v>577173</v>
       </c>
       <c r="R71" t="n">
-        <v>6711969</v>
+        <v>6711932</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8288,10 +8296,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125687119</v>
+        <v>125687129</v>
       </c>
       <c r="B72" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8318,7 +8326,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8332,10 +8340,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>577190</v>
+        <v>577096</v>
       </c>
       <c r="R72" t="n">
-        <v>6711913</v>
+        <v>6711969</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8394,10 +8402,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125687115</v>
+        <v>125687119</v>
       </c>
       <c r="B73" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8424,7 +8432,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8438,10 +8446,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>577167</v>
+        <v>577190</v>
       </c>
       <c r="R73" t="n">
-        <v>6711948</v>
+        <v>6711913</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8500,10 +8508,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125687120</v>
+        <v>125687115</v>
       </c>
       <c r="B74" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8530,7 +8538,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8538,23 +8546,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>577187</v>
+        <v>577167</v>
       </c>
       <c r="R74" t="n">
-        <v>6711920</v>
+        <v>6711948</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8595,7 +8596,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8614,32 +8614,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125687087</v>
+        <v>125687148</v>
       </c>
       <c r="B75" t="n">
-        <v>96596</v>
+        <v>98262</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>53</v>
+        <v>219790</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>577157</v>
+        <v>577163</v>
       </c>
       <c r="R75" t="n">
-        <v>6711975</v>
+        <v>6711969</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8711,54 +8711,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125687125</v>
+        <v>125687096</v>
       </c>
       <c r="B76" t="n">
-        <v>98343</v>
+        <v>103778</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>577172</v>
+        <v>577145</v>
       </c>
       <c r="R76" t="n">
-        <v>6711942</v>
+        <v>6711831</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8817,45 +8808,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125687148</v>
+        <v>125687125</v>
       </c>
       <c r="B77" t="n">
-        <v>98260</v>
+        <v>98345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>577163</v>
+        <v>577172</v>
       </c>
       <c r="R77" t="n">
-        <v>6711969</v>
+        <v>6711942</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8914,32 +8914,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125687096</v>
+        <v>125687087</v>
       </c>
       <c r="B78" t="n">
-        <v>103774</v>
+        <v>96598</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8949,10 +8949,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>577145</v>
+        <v>577157</v>
       </c>
       <c r="R78" t="n">
-        <v>6711831</v>
+        <v>6711975</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9011,45 +9011,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125687088</v>
+        <v>125687146</v>
       </c>
       <c r="B79" t="n">
-        <v>96596</v>
+        <v>98345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>577173</v>
+        <v>577165</v>
       </c>
       <c r="R79" t="n">
-        <v>6711943</v>
+        <v>6711956</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9108,50 +9117,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125687097</v>
+        <v>125687088</v>
       </c>
       <c r="B80" t="n">
-        <v>4772</v>
+        <v>96598</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>577154</v>
+        <v>577173</v>
       </c>
       <c r="R80" t="n">
-        <v>6711917</v>
+        <v>6711943</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9210,42 +9214,38 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125687146</v>
+        <v>125687097</v>
       </c>
       <c r="B81" t="n">
-        <v>98343</v>
+        <v>4772</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9254,10 +9254,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>577165</v>
+        <v>577154</v>
       </c>
       <c r="R81" t="n">
-        <v>6711956</v>
+        <v>6711917</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9319,7 +9319,7 @@
         <v>125687094</v>
       </c>
       <c r="B82" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>125687132</v>
       </c>
       <c r="B83" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>125687117</v>
       </c>
       <c r="B84" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9625,10 +9625,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125687118</v>
+        <v>125687135</v>
       </c>
       <c r="B85" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -9669,10 +9669,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>577129</v>
+        <v>577117</v>
       </c>
       <c r="R85" t="n">
-        <v>6711973</v>
+        <v>6712004</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9731,10 +9731,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125687135</v>
+        <v>125687118</v>
       </c>
       <c r="B86" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -9775,10 +9775,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>577117</v>
+        <v>577129</v>
       </c>
       <c r="R86" t="n">
-        <v>6712004</v>
+        <v>6711973</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -4552,7 +4552,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125687121</v>
+        <v>125687127</v>
       </c>
       <c r="B36" t="n">
         <v>98345</v>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4590,16 +4590,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577178</v>
+        <v>577095</v>
       </c>
       <c r="R36" t="n">
-        <v>6711912</v>
+        <v>6711970</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4640,6 +4647,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4658,7 +4666,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125687127</v>
+        <v>125687121</v>
       </c>
       <c r="B37" t="n">
         <v>98345</v>
@@ -4688,7 +4696,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4696,23 +4704,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577095</v>
+        <v>577178</v>
       </c>
       <c r="R37" t="n">
-        <v>6711970</v>
+        <v>6711912</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4753,7 +4754,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5788,45 +5788,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125687081</v>
+        <v>125687133</v>
       </c>
       <c r="B48" t="n">
-        <v>96598</v>
+        <v>98345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577109</v>
+        <v>577171</v>
       </c>
       <c r="R48" t="n">
-        <v>6711890</v>
+        <v>6711869</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5859,6 +5868,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5885,54 +5899,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125687133</v>
+        <v>125687081</v>
       </c>
       <c r="B49" t="n">
-        <v>98345</v>
+        <v>96598</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577171</v>
+        <v>577109</v>
       </c>
       <c r="R49" t="n">
-        <v>6711869</v>
+        <v>6711890</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5965,11 +5970,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6911,45 +6911,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125687085</v>
+        <v>125687114</v>
       </c>
       <c r="B59" t="n">
-        <v>96598</v>
+        <v>98345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>577130</v>
+        <v>577145</v>
       </c>
       <c r="R59" t="n">
-        <v>6711985</v>
+        <v>6711974</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7008,54 +7017,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125687114</v>
+        <v>125687085</v>
       </c>
       <c r="B60" t="n">
-        <v>98345</v>
+        <v>96598</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577145</v>
+        <v>577130</v>
       </c>
       <c r="R60" t="n">
-        <v>6711974</v>
+        <v>6711985</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8076,7 +8076,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125687120</v>
+        <v>125687126</v>
       </c>
       <c r="B70" t="n">
         <v>98345</v>
@@ -8114,23 +8114,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>577187</v>
+        <v>577173</v>
       </c>
       <c r="R70" t="n">
-        <v>6711920</v>
+        <v>6711932</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8171,7 +8164,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8190,7 +8182,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125687126</v>
+        <v>125687129</v>
       </c>
       <c r="B71" t="n">
         <v>98345</v>
@@ -8220,7 +8212,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8234,10 +8226,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>577173</v>
+        <v>577096</v>
       </c>
       <c r="R71" t="n">
-        <v>6711932</v>
+        <v>6711969</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8296,7 +8288,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125687129</v>
+        <v>125687120</v>
       </c>
       <c r="B72" t="n">
         <v>98345</v>
@@ -8326,7 +8318,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8334,16 +8326,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>577096</v>
+        <v>577187</v>
       </c>
       <c r="R72" t="n">
-        <v>6711969</v>
+        <v>6711920</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8384,6 +8383,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8614,10 +8614,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125687148</v>
+        <v>125687096</v>
       </c>
       <c r="B75" t="n">
-        <v>98262</v>
+        <v>103778</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8625,21 +8625,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219790</v>
+        <v>222412</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>577163</v>
+        <v>577145</v>
       </c>
       <c r="R75" t="n">
-        <v>6711969</v>
+        <v>6711831</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8711,32 +8711,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125687096</v>
+        <v>125687087</v>
       </c>
       <c r="B76" t="n">
-        <v>103778</v>
+        <v>96598</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8746,10 +8746,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>577145</v>
+        <v>577157</v>
       </c>
       <c r="R76" t="n">
-        <v>6711831</v>
+        <v>6711975</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8808,54 +8808,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125687125</v>
+        <v>125687148</v>
       </c>
       <c r="B77" t="n">
-        <v>98345</v>
+        <v>98262</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>577172</v>
+        <v>577163</v>
       </c>
       <c r="R77" t="n">
-        <v>6711942</v>
+        <v>6711969</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8914,45 +8905,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125687087</v>
+        <v>125687125</v>
       </c>
       <c r="B78" t="n">
-        <v>96598</v>
+        <v>98345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>577157</v>
+        <v>577172</v>
       </c>
       <c r="R78" t="n">
-        <v>6711975</v>
+        <v>6711942</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9011,54 +9011,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125687146</v>
+        <v>125687088</v>
       </c>
       <c r="B79" t="n">
-        <v>98345</v>
+        <v>96598</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>577165</v>
+        <v>577173</v>
       </c>
       <c r="R79" t="n">
-        <v>6711956</v>
+        <v>6711943</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9117,45 +9108,50 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125687088</v>
+        <v>125687097</v>
       </c>
       <c r="B80" t="n">
-        <v>96598</v>
+        <v>4772</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>577173</v>
+        <v>577154</v>
       </c>
       <c r="R80" t="n">
-        <v>6711943</v>
+        <v>6711917</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9214,38 +9210,42 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125687097</v>
+        <v>125687146</v>
       </c>
       <c r="B81" t="n">
-        <v>4772</v>
+        <v>98345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9254,10 +9254,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>577154</v>
+        <v>577165</v>
       </c>
       <c r="R81" t="n">
-        <v>6711917</v>
+        <v>6711956</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -3743,7 +3743,7 @@
         <v>125687083</v>
       </c>
       <c r="B28" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>125687078</v>
       </c>
       <c r="B29" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>125687111</v>
       </c>
       <c r="B30" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4040,54 +4040,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125687123</v>
+        <v>125687079</v>
       </c>
       <c r="B31" t="n">
-        <v>98345</v>
+        <v>96602</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577090</v>
+        <v>577171</v>
       </c>
       <c r="R31" t="n">
-        <v>6711978</v>
+        <v>6711847</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4146,10 +4137,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125687116</v>
+        <v>125687123</v>
       </c>
       <c r="B32" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4167,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4190,10 +4181,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577202</v>
+        <v>577090</v>
       </c>
       <c r="R32" t="n">
-        <v>6711890</v>
+        <v>6711978</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4255,7 +4246,7 @@
         <v>125687142</v>
       </c>
       <c r="B33" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4358,45 +4349,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125687079</v>
+        <v>125687116</v>
       </c>
       <c r="B34" t="n">
-        <v>96598</v>
+        <v>98349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577171</v>
+        <v>577202</v>
       </c>
       <c r="R34" t="n">
-        <v>6711847</v>
+        <v>6711890</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
         <v>125687086</v>
       </c>
       <c r="B35" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4552,10 +4552,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125687127</v>
+        <v>125687121</v>
       </c>
       <c r="B36" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4590,23 +4590,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577095</v>
+        <v>577178</v>
       </c>
       <c r="R36" t="n">
-        <v>6711970</v>
+        <v>6711912</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4647,7 +4640,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4666,10 +4658,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125687121</v>
+        <v>125687127</v>
       </c>
       <c r="B37" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4696,7 +4688,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4704,16 +4696,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577178</v>
+        <v>577095</v>
       </c>
       <c r="R37" t="n">
-        <v>6711912</v>
+        <v>6711970</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4754,6 +4753,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4772,50 +4772,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125687150</v>
+        <v>125687092</v>
       </c>
       <c r="B38" t="n">
-        <v>5176</v>
+        <v>91242</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577174</v>
+        <v>577169</v>
       </c>
       <c r="R38" t="n">
-        <v>6711873</v>
+        <v>6711859</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4874,45 +4869,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125687092</v>
+        <v>125687122</v>
       </c>
       <c r="B39" t="n">
-        <v>91238</v>
+        <v>98349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577169</v>
+        <v>577145</v>
       </c>
       <c r="R39" t="n">
-        <v>6711859</v>
+        <v>6711917</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4971,10 +4975,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125687122</v>
+        <v>125687130</v>
       </c>
       <c r="B40" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5001,7 +5005,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5015,10 +5019,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577145</v>
+        <v>577105</v>
       </c>
       <c r="R40" t="n">
-        <v>6711917</v>
+        <v>6711976</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5077,10 +5081,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125687130</v>
+        <v>125687140</v>
       </c>
       <c r="B41" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5107,7 +5111,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5121,10 +5125,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577105</v>
+        <v>577141</v>
       </c>
       <c r="R41" t="n">
-        <v>6711976</v>
+        <v>6711960</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5183,42 +5187,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125687140</v>
+        <v>125687150</v>
       </c>
       <c r="B42" t="n">
-        <v>98345</v>
+        <v>5176</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577141</v>
+        <v>577174</v>
       </c>
       <c r="R42" t="n">
-        <v>6711960</v>
+        <v>6711873</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5289,45 +5289,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125687093</v>
+        <v>125687145</v>
       </c>
       <c r="B43" t="n">
-        <v>91238</v>
+        <v>98349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577243</v>
+        <v>577155</v>
       </c>
       <c r="R43" t="n">
-        <v>6711783</v>
+        <v>6711978</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5386,10 +5395,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125687091</v>
+        <v>125687093</v>
       </c>
       <c r="B44" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5421,10 +5430,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577156</v>
+        <v>577243</v>
       </c>
       <c r="R44" t="n">
-        <v>6711864</v>
+        <v>6711783</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5483,50 +5492,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125687151</v>
+        <v>125687091</v>
       </c>
       <c r="B45" t="n">
-        <v>5176</v>
+        <v>91242</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577176</v>
+        <v>577156</v>
       </c>
       <c r="R45" t="n">
-        <v>6711840</v>
+        <v>6711864</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5588,7 +5592,7 @@
         <v>125687090</v>
       </c>
       <c r="B46" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5682,42 +5686,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125687145</v>
+        <v>125687151</v>
       </c>
       <c r="B47" t="n">
-        <v>98345</v>
+        <v>5176</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5726,10 +5726,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577155</v>
+        <v>577176</v>
       </c>
       <c r="R47" t="n">
-        <v>6711978</v>
+        <v>6711840</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5788,54 +5788,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125687133</v>
+        <v>125687081</v>
       </c>
       <c r="B48" t="n">
-        <v>98345</v>
+        <v>96602</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577171</v>
+        <v>577109</v>
       </c>
       <c r="R48" t="n">
-        <v>6711869</v>
+        <v>6711890</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5868,11 +5859,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5899,45 +5885,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125687081</v>
+        <v>125687133</v>
       </c>
       <c r="B49" t="n">
-        <v>96598</v>
+        <v>98349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577109</v>
+        <v>577171</v>
       </c>
       <c r="R49" t="n">
-        <v>6711890</v>
+        <v>6711869</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5970,6 +5965,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5999,7 +5999,7 @@
         <v>125687082</v>
       </c>
       <c r="B50" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>125687131</v>
       </c>
       <c r="B51" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>125687152</v>
       </c>
       <c r="B52" t="n">
-        <v>102574</v>
+        <v>102578</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>125687149</v>
       </c>
       <c r="B53" t="n">
-        <v>95197</v>
+        <v>95201</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>125687084</v>
       </c>
       <c r="B54" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>125687139</v>
       </c>
       <c r="B55" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>125687136</v>
       </c>
       <c r="B56" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>125687095</v>
       </c>
       <c r="B57" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>125687143</v>
       </c>
       <c r="B58" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>125687114</v>
       </c>
       <c r="B59" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>125687085</v>
       </c>
       <c r="B60" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>125687141</v>
       </c>
       <c r="B61" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7220,10 +7220,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125687144</v>
+        <v>125687113</v>
       </c>
       <c r="B62" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7264,10 +7264,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577150</v>
+        <v>577142</v>
       </c>
       <c r="R62" t="n">
-        <v>6711962</v>
+        <v>6711971</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7326,10 +7326,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125687110</v>
+        <v>125687144</v>
       </c>
       <c r="B63" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7364,23 +7364,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577101</v>
+        <v>577150</v>
       </c>
       <c r="R63" t="n">
-        <v>6711989</v>
+        <v>6711962</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7421,7 +7414,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7443,7 +7435,7 @@
         <v>125687128</v>
       </c>
       <c r="B64" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7546,10 +7538,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125687113</v>
+        <v>125687110</v>
       </c>
       <c r="B65" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7568,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7584,16 +7576,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>577142</v>
+        <v>577101</v>
       </c>
       <c r="R65" t="n">
-        <v>6711971</v>
+        <v>6711989</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7634,6 +7633,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7655,7 +7655,7 @@
         <v>125687112</v>
       </c>
       <c r="B66" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>125687134</v>
       </c>
       <c r="B67" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7864,10 +7864,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125687124</v>
+        <v>125687137</v>
       </c>
       <c r="B68" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7908,10 +7908,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>577103</v>
+        <v>577195</v>
       </c>
       <c r="R68" t="n">
-        <v>6711980</v>
+        <v>6711896</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7970,10 +7970,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125687137</v>
+        <v>125687124</v>
       </c>
       <c r="B69" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>577195</v>
+        <v>577103</v>
       </c>
       <c r="R69" t="n">
-        <v>6711896</v>
+        <v>6711980</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8076,10 +8076,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125687126</v>
+        <v>125687120</v>
       </c>
       <c r="B70" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8114,16 +8114,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>577173</v>
+        <v>577187</v>
       </c>
       <c r="R70" t="n">
-        <v>6711932</v>
+        <v>6711920</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8164,6 +8171,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8182,10 +8190,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125687129</v>
+        <v>125687119</v>
       </c>
       <c r="B71" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8212,7 +8220,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8226,10 +8234,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>577096</v>
+        <v>577190</v>
       </c>
       <c r="R71" t="n">
-        <v>6711969</v>
+        <v>6711913</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8288,10 +8296,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125687120</v>
+        <v>125687126</v>
       </c>
       <c r="B72" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8326,23 +8334,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>577187</v>
+        <v>577173</v>
       </c>
       <c r="R72" t="n">
-        <v>6711920</v>
+        <v>6711932</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8383,7 +8384,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8402,10 +8402,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125687119</v>
+        <v>125687129</v>
       </c>
       <c r="B73" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8446,10 +8446,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>577190</v>
+        <v>577096</v>
       </c>
       <c r="R73" t="n">
-        <v>6711913</v>
+        <v>6711969</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8511,7 +8511,7 @@
         <v>125687115</v>
       </c>
       <c r="B74" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8614,45 +8614,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125687096</v>
+        <v>125687125</v>
       </c>
       <c r="B75" t="n">
-        <v>103778</v>
+        <v>98349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>577145</v>
+        <v>577172</v>
       </c>
       <c r="R75" t="n">
-        <v>6711831</v>
+        <v>6711942</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8711,32 +8720,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125687087</v>
+        <v>125687148</v>
       </c>
       <c r="B76" t="n">
-        <v>96598</v>
+        <v>98266</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>53</v>
+        <v>219790</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8746,10 +8755,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>577157</v>
+        <v>577163</v>
       </c>
       <c r="R76" t="n">
-        <v>6711975</v>
+        <v>6711969</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8808,32 +8817,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125687148</v>
+        <v>125687087</v>
       </c>
       <c r="B77" t="n">
-        <v>98262</v>
+        <v>96602</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219790</v>
+        <v>53</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8843,10 +8852,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>577163</v>
+        <v>577157</v>
       </c>
       <c r="R77" t="n">
-        <v>6711969</v>
+        <v>6711975</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8905,54 +8914,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125687125</v>
+        <v>125687096</v>
       </c>
       <c r="B78" t="n">
-        <v>98345</v>
+        <v>103791</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>577172</v>
+        <v>577145</v>
       </c>
       <c r="R78" t="n">
-        <v>6711942</v>
+        <v>6711831</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9014,7 +9014,7 @@
         <v>125687088</v>
       </c>
       <c r="B79" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>125687146</v>
       </c>
       <c r="B81" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>125687094</v>
       </c>
       <c r="B82" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9413,10 +9413,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125687132</v>
+        <v>125687117</v>
       </c>
       <c r="B83" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>577153</v>
+        <v>577124</v>
       </c>
       <c r="R83" t="n">
         <v>6711978</v>
@@ -9519,10 +9519,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125687117</v>
+        <v>125687132</v>
       </c>
       <c r="B84" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>577124</v>
+        <v>577153</v>
       </c>
       <c r="R84" t="n">
         <v>6711978</v>
@@ -9625,10 +9625,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125687135</v>
+        <v>125687118</v>
       </c>
       <c r="B85" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -9669,10 +9669,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>577117</v>
+        <v>577129</v>
       </c>
       <c r="R85" t="n">
-        <v>6712004</v>
+        <v>6711973</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9731,10 +9731,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125687118</v>
+        <v>125687135</v>
       </c>
       <c r="B86" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -9775,10 +9775,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>577129</v>
+        <v>577117</v>
       </c>
       <c r="R86" t="n">
-        <v>6711973</v>
+        <v>6712004</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -4772,45 +4772,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125687092</v>
+        <v>125687150</v>
       </c>
       <c r="B38" t="n">
-        <v>91242</v>
+        <v>5176</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577169</v>
+        <v>577174</v>
       </c>
       <c r="R38" t="n">
-        <v>6711859</v>
+        <v>6711873</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4869,54 +4874,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125687122</v>
+        <v>125687092</v>
       </c>
       <c r="B39" t="n">
-        <v>98349</v>
+        <v>91242</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577145</v>
+        <v>577169</v>
       </c>
       <c r="R39" t="n">
-        <v>6711917</v>
+        <v>6711859</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4975,7 +4971,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125687130</v>
+        <v>125687122</v>
       </c>
       <c r="B40" t="n">
         <v>98349</v>
@@ -5005,7 +5001,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5019,10 +5015,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577105</v>
+        <v>577145</v>
       </c>
       <c r="R40" t="n">
-        <v>6711976</v>
+        <v>6711917</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5081,7 +5077,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125687140</v>
+        <v>125687130</v>
       </c>
       <c r="B41" t="n">
         <v>98349</v>
@@ -5111,7 +5107,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5125,10 +5121,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577141</v>
+        <v>577105</v>
       </c>
       <c r="R41" t="n">
-        <v>6711960</v>
+        <v>6711976</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5187,38 +5183,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125687150</v>
+        <v>125687140</v>
       </c>
       <c r="B42" t="n">
-        <v>5176</v>
+        <v>98349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577174</v>
+        <v>577141</v>
       </c>
       <c r="R42" t="n">
-        <v>6711873</v>
+        <v>6711960</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6708,45 +6708,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125687095</v>
+        <v>125687143</v>
       </c>
       <c r="B57" t="n">
-        <v>91242</v>
+        <v>98349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>577135</v>
+        <v>577152</v>
       </c>
       <c r="R57" t="n">
-        <v>6711824</v>
+        <v>6711960</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6805,54 +6814,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125687143</v>
+        <v>125687095</v>
       </c>
       <c r="B58" t="n">
-        <v>98349</v>
+        <v>91242</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>577152</v>
+        <v>577135</v>
       </c>
       <c r="R58" t="n">
-        <v>6711960</v>
+        <v>6711824</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -3743,7 +3743,7 @@
         <v>125687083</v>
       </c>
       <c r="B28" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>125687078</v>
       </c>
       <c r="B29" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>125687111</v>
       </c>
       <c r="B30" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>125687079</v>
       </c>
       <c r="B31" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4137,10 +4137,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125687123</v>
+        <v>125687142</v>
       </c>
       <c r="B32" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4181,10 +4181,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577090</v>
+        <v>577150</v>
       </c>
       <c r="R32" t="n">
-        <v>6711978</v>
+        <v>6711955</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4243,10 +4243,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125687142</v>
+        <v>125687123</v>
       </c>
       <c r="B33" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577150</v>
+        <v>577090</v>
       </c>
       <c r="R33" t="n">
-        <v>6711955</v>
+        <v>6711978</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4352,7 +4352,7 @@
         <v>125687116</v>
       </c>
       <c r="B34" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>125687086</v>
       </c>
       <c r="B35" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>125687121</v>
       </c>
       <c r="B36" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>125687127</v>
       </c>
       <c r="B37" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>125687122</v>
       </c>
       <c r="B40" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>125687130</v>
       </c>
       <c r="B41" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>125687140</v>
       </c>
       <c r="B42" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5289,42 +5289,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125687145</v>
+        <v>125687151</v>
       </c>
       <c r="B43" t="n">
-        <v>98349</v>
+        <v>5176</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5333,10 +5329,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577155</v>
+        <v>577176</v>
       </c>
       <c r="R43" t="n">
-        <v>6711978</v>
+        <v>6711840</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5686,38 +5682,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125687151</v>
+        <v>125687145</v>
       </c>
       <c r="B47" t="n">
-        <v>5176</v>
+        <v>98352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5726,10 +5726,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577176</v>
+        <v>577155</v>
       </c>
       <c r="R47" t="n">
-        <v>6711840</v>
+        <v>6711978</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5791,7 +5791,7 @@
         <v>125687081</v>
       </c>
       <c r="B48" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>125687133</v>
       </c>
       <c r="B49" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>125687082</v>
       </c>
       <c r="B50" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6093,54 +6093,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125687131</v>
+        <v>125687152</v>
       </c>
       <c r="B51" t="n">
-        <v>98349</v>
+        <v>102581</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>223246</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577148</v>
+        <v>577131</v>
       </c>
       <c r="R51" t="n">
-        <v>6711976</v>
+        <v>6711836</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6175,12 +6166,18 @@
           <t>2025-06-04</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>12 cm dbh</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6199,45 +6196,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125687152</v>
+        <v>125687131</v>
       </c>
       <c r="B52" t="n">
-        <v>102578</v>
+        <v>98352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>223246</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577131</v>
+        <v>577148</v>
       </c>
       <c r="R52" t="n">
-        <v>6711836</v>
+        <v>6711976</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6272,18 +6278,12 @@
           <t>2025-06-04</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>12 cm dbh</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6305,7 +6305,7 @@
         <v>125687149</v>
       </c>
       <c r="B53" t="n">
-        <v>95201</v>
+        <v>95204</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6399,45 +6399,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125687084</v>
+        <v>125687136</v>
       </c>
       <c r="B54" t="n">
-        <v>96602</v>
+        <v>98352</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577088</v>
+        <v>577187</v>
       </c>
       <c r="R54" t="n">
-        <v>6711963</v>
+        <v>6711916</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6499,7 +6508,7 @@
         <v>125687139</v>
       </c>
       <c r="B55" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6602,54 +6611,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125687136</v>
+        <v>125687084</v>
       </c>
       <c r="B56" t="n">
-        <v>98349</v>
+        <v>96605</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>577187</v>
+        <v>577088</v>
       </c>
       <c r="R56" t="n">
-        <v>6711916</v>
+        <v>6711963</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6708,54 +6708,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125687143</v>
+        <v>125687095</v>
       </c>
       <c r="B57" t="n">
-        <v>98349</v>
+        <v>91242</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>577152</v>
+        <v>577135</v>
       </c>
       <c r="R57" t="n">
-        <v>6711960</v>
+        <v>6711824</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6814,45 +6805,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125687095</v>
+        <v>125687143</v>
       </c>
       <c r="B58" t="n">
-        <v>91242</v>
+        <v>98352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>577135</v>
+        <v>577152</v>
       </c>
       <c r="R58" t="n">
-        <v>6711824</v>
+        <v>6711960</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6911,54 +6911,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125687114</v>
+        <v>125687085</v>
       </c>
       <c r="B59" t="n">
-        <v>98349</v>
+        <v>96605</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>577145</v>
+        <v>577130</v>
       </c>
       <c r="R59" t="n">
-        <v>6711974</v>
+        <v>6711985</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7017,45 +7008,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125687085</v>
+        <v>125687114</v>
       </c>
       <c r="B60" t="n">
-        <v>96602</v>
+        <v>98352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577130</v>
+        <v>577145</v>
       </c>
       <c r="R60" t="n">
-        <v>6711985</v>
+        <v>6711974</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7117,7 +7117,7 @@
         <v>125687141</v>
       </c>
       <c r="B61" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7220,10 +7220,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125687113</v>
+        <v>125687128</v>
       </c>
       <c r="B62" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7264,10 +7264,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577142</v>
+        <v>577194</v>
       </c>
       <c r="R62" t="n">
-        <v>6711971</v>
+        <v>6711897</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7326,10 +7326,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125687144</v>
+        <v>125687110</v>
       </c>
       <c r="B63" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7364,16 +7364,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577150</v>
+        <v>577101</v>
       </c>
       <c r="R63" t="n">
-        <v>6711962</v>
+        <v>6711989</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7414,6 +7421,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7432,10 +7440,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125687128</v>
+        <v>125687113</v>
       </c>
       <c r="B64" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7462,7 +7470,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7476,10 +7484,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>577194</v>
+        <v>577142</v>
       </c>
       <c r="R64" t="n">
-        <v>6711897</v>
+        <v>6711971</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7538,10 +7546,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125687110</v>
+        <v>125687144</v>
       </c>
       <c r="B65" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7568,7 +7576,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7576,23 +7584,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>577101</v>
+        <v>577150</v>
       </c>
       <c r="R65" t="n">
-        <v>6711989</v>
+        <v>6711962</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7633,7 +7634,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7655,7 +7655,7 @@
         <v>125687112</v>
       </c>
       <c r="B66" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>125687134</v>
       </c>
       <c r="B67" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7864,10 +7864,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125687137</v>
+        <v>125687124</v>
       </c>
       <c r="B68" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7908,10 +7908,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>577195</v>
+        <v>577103</v>
       </c>
       <c r="R68" t="n">
-        <v>6711896</v>
+        <v>6711980</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7970,10 +7970,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125687124</v>
+        <v>125687137</v>
       </c>
       <c r="B69" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>577103</v>
+        <v>577195</v>
       </c>
       <c r="R69" t="n">
-        <v>6711980</v>
+        <v>6711896</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8076,10 +8076,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125687120</v>
+        <v>125687126</v>
       </c>
       <c r="B70" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8114,23 +8114,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>577187</v>
+        <v>577173</v>
       </c>
       <c r="R70" t="n">
-        <v>6711920</v>
+        <v>6711932</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8171,7 +8164,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8190,10 +8182,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125687119</v>
+        <v>125687129</v>
       </c>
       <c r="B71" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8220,7 +8212,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8234,10 +8226,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>577190</v>
+        <v>577096</v>
       </c>
       <c r="R71" t="n">
-        <v>6711913</v>
+        <v>6711969</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8296,10 +8288,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125687126</v>
+        <v>125687119</v>
       </c>
       <c r="B72" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8326,7 +8318,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8340,10 +8332,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>577173</v>
+        <v>577190</v>
       </c>
       <c r="R72" t="n">
-        <v>6711932</v>
+        <v>6711913</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8402,10 +8394,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125687129</v>
+        <v>125687115</v>
       </c>
       <c r="B73" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8432,7 +8424,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8446,10 +8438,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>577096</v>
+        <v>577167</v>
       </c>
       <c r="R73" t="n">
-        <v>6711969</v>
+        <v>6711948</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8508,10 +8500,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125687115</v>
+        <v>125687120</v>
       </c>
       <c r="B74" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8538,7 +8530,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8546,16 +8538,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>577167</v>
+        <v>577187</v>
       </c>
       <c r="R74" t="n">
-        <v>6711948</v>
+        <v>6711920</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8596,6 +8595,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8614,54 +8614,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125687125</v>
+        <v>125687087</v>
       </c>
       <c r="B75" t="n">
-        <v>98349</v>
+        <v>96605</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>577172</v>
+        <v>577157</v>
       </c>
       <c r="R75" t="n">
-        <v>6711942</v>
+        <v>6711975</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8723,7 +8714,7 @@
         <v>125687148</v>
       </c>
       <c r="B76" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8817,45 +8808,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125687087</v>
+        <v>125687125</v>
       </c>
       <c r="B77" t="n">
-        <v>96602</v>
+        <v>98352</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>577157</v>
+        <v>577172</v>
       </c>
       <c r="R77" t="n">
-        <v>6711975</v>
+        <v>6711942</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8917,7 +8917,7 @@
         <v>125687096</v>
       </c>
       <c r="B78" t="n">
-        <v>103791</v>
+        <v>103794</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>125687088</v>
       </c>
       <c r="B79" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>125687146</v>
       </c>
       <c r="B81" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9413,10 +9413,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125687117</v>
+        <v>125687132</v>
       </c>
       <c r="B83" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>577124</v>
+        <v>577153</v>
       </c>
       <c r="R83" t="n">
         <v>6711978</v>
@@ -9519,10 +9519,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125687132</v>
+        <v>125687117</v>
       </c>
       <c r="B84" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>577153</v>
+        <v>577124</v>
       </c>
       <c r="R84" t="n">
         <v>6711978</v>
@@ -9628,7 +9628,7 @@
         <v>125687118</v>
       </c>
       <c r="B85" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>125687135</v>
       </c>
       <c r="B86" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY86"/>
+  <dimension ref="A1:AY90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9835,6 +9835,414 @@
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>131983559</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99046</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>577133</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6711890</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>131983662</v>
+      </c>
+      <c r="B88" t="n">
+        <v>96266</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>577133</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6711890</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>131989456</v>
+      </c>
+      <c r="B89" t="n">
+        <v>97522</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>2563</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Terpentinmossa</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Geocalyx graveolens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Schrad.) Nees</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>577172</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6711877</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Lövlåga intill äldre dike</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>131983736</v>
+      </c>
+      <c r="B90" t="n">
+        <v>97286</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>53</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>577111</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6711904</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AY89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10031,52 +10031,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131989456</v>
+        <v>131983736</v>
       </c>
       <c r="B89" t="n">
-        <v>97522</v>
+        <v>97286</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2563</v>
+        <v>53</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Terpentinmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Geocalyx graveolens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schrad.) Nees</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>577172</v>
+        <v>577111</v>
       </c>
       <c r="R89" t="n">
-        <v>6711877</v>
+        <v>6711904</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10114,24 +10110,8 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Lövlåga intill äldre dike</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -10145,103 +10125,6 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>131983736</v>
-      </c>
-      <c r="B90" t="n">
-        <v>97286</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>53</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Lars-Lars fäbod, Gstr</t>
-        </is>
-      </c>
-      <c r="Q90" t="n">
-        <v>577111</v>
-      </c>
-      <c r="R90" t="n">
-        <v>6711904</v>
-      </c>
-      <c r="S90" t="n">
-        <v>5</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Hofors</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Gästrikland</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Torsåker</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AD90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT90" t="inlineStr"/>
-      <c r="AW90" t="inlineStr">
-        <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -9840,7 +9840,7 @@
         <v>131983559</v>
       </c>
       <c r="B87" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>131983662</v>
       </c>
       <c r="B88" t="n">
-        <v>96266</v>
+        <v>96267</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>131983736</v>
       </c>
       <c r="B89" t="n">
-        <v>97286</v>
+        <v>97287</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -9840,7 +9840,7 @@
         <v>131983559</v>
       </c>
       <c r="B87" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>131983662</v>
       </c>
       <c r="B88" t="n">
-        <v>96267</v>
+        <v>96272</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>131983736</v>
       </c>
       <c r="B89" t="n">
-        <v>97287</v>
+        <v>97292</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -9840,7 +9840,7 @@
         <v>131983559</v>
       </c>
       <c r="B87" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>131983662</v>
       </c>
       <c r="B88" t="n">
-        <v>96315</v>
+        <v>96318</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>131983736</v>
       </c>
       <c r="B89" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -9840,7 +9840,7 @@
         <v>131983559</v>
       </c>
       <c r="B87" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>131983662</v>
       </c>
       <c r="B88" t="n">
-        <v>96318</v>
+        <v>96326</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>131983736</v>
       </c>
       <c r="B89" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -9840,7 +9840,7 @@
         <v>131983559</v>
       </c>
       <c r="B87" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>131983662</v>
       </c>
       <c r="B88" t="n">
-        <v>96326</v>
+        <v>96336</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>131983736</v>
       </c>
       <c r="B89" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -9840,7 +9840,7 @@
         <v>131983559</v>
       </c>
       <c r="B87" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>131983662</v>
       </c>
       <c r="B88" t="n">
-        <v>96336</v>
+        <v>96338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>131983736</v>
       </c>
       <c r="B89" t="n">
-        <v>97356</v>
+        <v>97358</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1052853</v>
+        <v>57642289</v>
       </c>
       <c r="B2" t="n">
-        <v>83135</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3518</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Barkhyttsvägen, Gstr</t>
+          <t>Linderåsgruvan 2, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577146.9258164363</v>
+        <v>577138</v>
       </c>
       <c r="R2" t="n">
-        <v>6711939.519736157</v>
+        <v>6711909</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-08-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,57 +762,48 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>lövträdslågor, mossa</t>
-        </is>
-      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lena Melin</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lena Melin</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>57642282</v>
+        <v>57642290</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577226.0127935157</v>
+        <v>577148</v>
       </c>
       <c r="R3" t="n">
-        <v>6711815.185534686</v>
+        <v>6711957</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -874,19 +846,9 @@
           <t>2014-09-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -919,53 +881,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>57642304</v>
+        <v>103306856</v>
       </c>
       <c r="B4" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 2, Gstr</t>
+          <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577113.9815424266</v>
+        <v>577103</v>
       </c>
       <c r="R4" t="n">
-        <v>6711865.958189813</v>
+        <v>6711856</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,27 +948,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,69 +975,65 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>57642279</v>
+        <v>103307766</v>
       </c>
       <c r="B5" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 2, Gstr</t>
+          <t>Barkhyttevägen 40, Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577214.8012728965</v>
+        <v>577149</v>
       </c>
       <c r="R5" t="n">
-        <v>6711832.175986194</v>
+        <v>6711850</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,27 +1057,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,69 +1084,63 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AR5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>57642294</v>
+        <v>125687078</v>
       </c>
       <c r="B6" t="n">
-        <v>93056</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2813</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 2, Gstr</t>
+          <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577150.7676112134</v>
+        <v>577169</v>
       </c>
       <c r="R6" t="n">
-        <v>6711875.112995247</v>
+        <v>6711894</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,27 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,69 +1181,63 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AR6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>57642292</v>
+        <v>125687079</v>
       </c>
       <c r="B7" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 2, Gstr</t>
+          <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577198.8539099756</v>
+        <v>577171</v>
       </c>
       <c r="R7" t="n">
-        <v>6711793.928276244</v>
+        <v>6711847</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1343,27 +1261,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,69 +1278,63 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AR7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>57642303</v>
+        <v>125687080</v>
       </c>
       <c r="B8" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 2, Gstr</t>
+          <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577184.9813545226</v>
+        <v>577154</v>
       </c>
       <c r="R8" t="n">
-        <v>6711773.939736401</v>
+        <v>6711790</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,27 +1358,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,69 +1375,63 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>57642280</v>
+        <v>125687081</v>
       </c>
       <c r="B9" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 2, Gstr</t>
+          <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577142.1786487412</v>
+        <v>577109</v>
       </c>
       <c r="R9" t="n">
-        <v>6711884.775154659</v>
+        <v>6711890</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1579,27 +1455,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,69 +1472,63 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AR9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>57642281</v>
+        <v>125687082</v>
       </c>
       <c r="B10" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 2, Gstr</t>
+          <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577207.0049041801</v>
+        <v>577110</v>
       </c>
       <c r="R10" t="n">
-        <v>6711896.991188557</v>
+        <v>6711911</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1697,27 +1552,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,69 +1569,63 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AR10" t="inlineStr"/>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>57642302</v>
+        <v>125687083</v>
       </c>
       <c r="B11" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3762</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 2, Gstr</t>
+          <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577133.066585777</v>
+        <v>577154</v>
       </c>
       <c r="R11" t="n">
-        <v>6711872.765619252</v>
+        <v>6711905</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1815,27 +1649,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,31 +1666,25 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AR11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>57642289</v>
+        <v>125687084</v>
       </c>
       <c r="B12" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,17 +1712,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 2, Gstr</t>
+          <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577138.2134367358</v>
+        <v>577088</v>
       </c>
       <c r="R12" t="n">
-        <v>6711908.812274798</v>
+        <v>6711963</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1933,27 +1746,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,69 +1763,63 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AR12" t="inlineStr"/>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>57642283</v>
+        <v>125687085</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 2, Gstr</t>
+          <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577103.9666159069</v>
+        <v>577130</v>
       </c>
       <c r="R13" t="n">
-        <v>6711873.12857515</v>
+        <v>6711985</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2051,27 +1843,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,31 +1860,25 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AR13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>57642290</v>
+        <v>125687086</v>
       </c>
       <c r="B14" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2135,17 +1906,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 2, Gstr</t>
+          <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577148.0363469627</v>
+        <v>577150</v>
       </c>
       <c r="R14" t="n">
-        <v>6711956.773116669</v>
+        <v>6711955</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2169,27 +1940,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2201,69 +1957,63 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AR14" t="inlineStr"/>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>57642300</v>
+        <v>125687087</v>
       </c>
       <c r="B15" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3674</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 2, Gstr</t>
+          <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577143.7623799909</v>
+        <v>577157</v>
       </c>
       <c r="R15" t="n">
-        <v>6711879.88615043</v>
+        <v>6711975</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2287,27 +2037,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2319,69 +2054,63 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AR15" t="inlineStr"/>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>57642249</v>
+        <v>125687088</v>
       </c>
       <c r="B16" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 1, Gstr</t>
+          <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577135.7621991078</v>
+        <v>577173</v>
       </c>
       <c r="R16" t="n">
-        <v>6711861.992908971</v>
+        <v>6711943</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2405,27 +2134,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2437,69 +2151,63 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AR16" t="inlineStr"/>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>57642293</v>
+        <v>131983736</v>
       </c>
       <c r="B17" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97435</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2809</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 2, Gstr</t>
+          <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577113.8133748735</v>
+        <v>577111</v>
       </c>
       <c r="R17" t="n">
-        <v>6711873.831174828</v>
+        <v>6711904</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2523,27 +2231,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2555,53 +2248,47 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AR17" t="inlineStr"/>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>57642278</v>
+        <v>57642307</v>
       </c>
       <c r="B18" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222412</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2611,10 +2298,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577171.1778314661</v>
+        <v>577187</v>
       </c>
       <c r="R18" t="n">
-        <v>6711819.920516795</v>
+        <v>6711803</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2644,19 +2331,9 @@
           <t>2014-09-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2689,53 +2366,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>57642305</v>
+        <v>125687091</v>
       </c>
       <c r="B19" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 2, Gstr</t>
+          <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577154.8184501601</v>
+        <v>577156</v>
       </c>
       <c r="R19" t="n">
-        <v>6711824.001498986</v>
+        <v>6711864</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2759,27 +2431,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2791,69 +2448,63 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AR19" t="inlineStr"/>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>57642299</v>
+        <v>125687092</v>
       </c>
       <c r="B20" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 2, Gstr</t>
+          <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577152.8035346523</v>
+        <v>577169</v>
       </c>
       <c r="R20" t="n">
-        <v>6711849.065272661</v>
+        <v>6711859</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2877,27 +2528,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2909,76 +2545,63 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AR20" t="inlineStr"/>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>88898115</v>
+        <v>125687093</v>
       </c>
       <c r="B21" t="n">
-        <v>86134</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4377</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blodvaxskivling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Barkhyttsvägen, Gstr</t>
+          <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577218.0303394456</v>
+        <v>577243</v>
       </c>
       <c r="R21" t="n">
-        <v>6711842.583164816</v>
+        <v>6711783</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3002,22 +2625,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3026,34 +2639,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lena Melin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lena Melin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103306856</v>
+        <v>125687094</v>
       </c>
       <c r="B22" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3061,39 +2668,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hofors, Gstr</t>
+          <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577103.8310608319</v>
+        <v>577189</v>
       </c>
       <c r="R22" t="n">
-        <v>6711856.387932341</v>
+        <v>6711814</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3117,22 +2722,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3159,55 +2754,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103307641</v>
+        <v>125687095</v>
       </c>
       <c r="B23" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hofors, Gstr</t>
+          <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577106.0714404478</v>
+        <v>577135</v>
       </c>
       <c r="R23" t="n">
-        <v>6711936.185534708</v>
+        <v>6711824</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3231,27 +2819,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>I källpåverkat område</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3278,15 +2851,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103307852</v>
+        <v>125687149</v>
       </c>
       <c r="B24" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95957</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3294,38 +2862,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>2383</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Barkhyttevägen 40, Hofors, Gstr</t>
+          <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577221.8890800874</v>
+        <v>577165</v>
       </c>
       <c r="R24" t="n">
-        <v>6711846.604022142</v>
+        <v>6711852</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3349,22 +2916,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>16:04</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>16:04</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3394,12 +2951,7 @@
         <v>103307676</v>
       </c>
       <c r="B25" t="n">
-        <v>92688</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3433,10 +2985,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577106.0714404478</v>
+        <v>577106</v>
       </c>
       <c r="R25" t="n">
-        <v>6711936.185534708</v>
+        <v>6711937</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3505,55 +3057,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103307766</v>
+        <v>57642292</v>
       </c>
       <c r="B26" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>2809</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Barkhyttevägen 40, Hofors, Gstr</t>
+          <t>Linderåsgruvan 2, Gstr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577148.8185392596</v>
+        <v>577199</v>
       </c>
       <c r="R26" t="n">
-        <v>6711850.949268804</v>
+        <v>6711794</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3577,22 +3122,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3604,77 +3144,64 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
+      <c r="AR26" t="inlineStr"/>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125512020</v>
+        <v>57642293</v>
       </c>
       <c r="B27" t="n">
-        <v>98343</v>
+        <v>96338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Lars-Lars fäbod, Gstr</t>
+          <t>Linderåsgruvan 2, Gstr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577196</v>
+        <v>577114</v>
       </c>
       <c r="R27" t="n">
-        <v>6711856</v>
+        <v>6711874</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3698,22 +3225,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:44</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:44</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3725,47 +3247,48 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AR27" t="inlineStr"/>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Margareta Kling</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Margareta Kling</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125687083</v>
+        <v>131983662</v>
       </c>
       <c r="B28" t="n">
-        <v>96605</v>
+        <v>96413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>2809</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3775,10 +3298,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577154</v>
+        <v>577133</v>
       </c>
       <c r="R28" t="n">
-        <v>6711905</v>
+        <v>6711890</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3805,12 +3328,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3825,60 +3348,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125687078</v>
+        <v>57642294</v>
       </c>
       <c r="B29" t="n">
-        <v>96605</v>
+        <v>96350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>2813</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Gstr</t>
+          <t>Linderåsgruvan 2, Gstr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577169</v>
+        <v>577151</v>
       </c>
       <c r="R29" t="n">
-        <v>6711894</v>
+        <v>6711875</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3902,12 +3425,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3919,72 +3447,64 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AR29" t="inlineStr"/>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125687111</v>
+        <v>57642299</v>
       </c>
       <c r="B30" t="n">
-        <v>98352</v>
+        <v>91680</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Gstr</t>
+          <t>Linderåsgruvan 2, Gstr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577182</v>
+        <v>577153</v>
       </c>
       <c r="R30" t="n">
-        <v>6711920</v>
+        <v>6711849</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4008,12 +3528,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4025,63 +3550,73 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AR30" t="inlineStr"/>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125687079</v>
+        <v>1052853</v>
       </c>
       <c r="B31" t="n">
-        <v>96605</v>
+        <v>85274</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>3518</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Gstr</t>
+          <t>Barkhyttsvägen, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577171</v>
+        <v>577147</v>
       </c>
       <c r="R31" t="n">
-        <v>6711847</v>
+        <v>6711940</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4105,12 +3640,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2010-08-28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4121,73 +3656,69 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>lövträdslågor, mossa</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125687142</v>
+        <v>57642300</v>
       </c>
       <c r="B32" t="n">
-        <v>98352</v>
+        <v>87309</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>3674</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Gstr</t>
+          <t>Linderåsgruvan 2, Gstr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577150</v>
+        <v>577144</v>
       </c>
       <c r="R32" t="n">
-        <v>6711955</v>
+        <v>6711880</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4211,12 +3742,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4228,72 +3764,64 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AR32" t="inlineStr"/>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125687123</v>
+        <v>57642302</v>
       </c>
       <c r="B33" t="n">
-        <v>98352</v>
+        <v>87146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>3762</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Gstr</t>
+          <t>Linderåsgruvan 2, Gstr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577090</v>
+        <v>577133</v>
       </c>
       <c r="R33" t="n">
-        <v>6711978</v>
+        <v>6711873</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4317,12 +3845,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4334,72 +3867,64 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
+      <c r="AR33" t="inlineStr"/>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125687116</v>
+        <v>57642303</v>
       </c>
       <c r="B34" t="n">
-        <v>98352</v>
+        <v>93209</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Gstr</t>
+          <t>Linderåsgruvan 2, Gstr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577202</v>
+        <v>577185</v>
       </c>
       <c r="R34" t="n">
-        <v>6711890</v>
+        <v>6711774</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4423,12 +3948,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4440,25 +3970,26 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
+      <c r="AR34" t="inlineStr"/>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125687086</v>
+        <v>57642304</v>
       </c>
       <c r="B35" t="n">
-        <v>96605</v>
+        <v>93209</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4466,37 +3997,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>4366</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Gstr</t>
+          <t>Linderåsgruvan 2, Gstr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577150</v>
+        <v>577114</v>
       </c>
       <c r="R35" t="n">
-        <v>6711955</v>
+        <v>6711866</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4520,12 +4051,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4537,72 +4073,71 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
+      <c r="AR35" t="inlineStr"/>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125687121</v>
+        <v>88898115</v>
       </c>
       <c r="B36" t="n">
-        <v>98352</v>
+        <v>89083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>4377</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodvaxing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrocybe coccinea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Gstr</t>
+          <t>Barkhyttsvägen, Gstr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577178</v>
+        <v>577218</v>
       </c>
       <c r="R36" t="n">
-        <v>6711912</v>
+        <v>6711843</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4626,12 +4161,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4640,82 +4175,67 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125687127</v>
+        <v>57642305</v>
       </c>
       <c r="B37" t="n">
-        <v>98352</v>
+        <v>92869</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Gstr</t>
+          <t>Linderåsgruvan 2, Gstr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577095</v>
+        <v>577155</v>
       </c>
       <c r="R37" t="n">
-        <v>6711970</v>
+        <v>6711824</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4739,12 +4259,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4753,29 +4278,29 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
+      <c r="AR37" t="inlineStr"/>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125687150</v>
+        <v>103307852</v>
       </c>
       <c r="B38" t="n">
-        <v>5176</v>
+        <v>91872</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4783,42 +4308,38 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Gstr</t>
+          <t>Barkhyttevägen 40, Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577174</v>
+        <v>577222</v>
       </c>
       <c r="R38" t="n">
-        <v>6711873</v>
+        <v>6711847</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4842,12 +4363,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4874,32 +4405,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125687092</v>
+        <v>125687090</v>
       </c>
       <c r="B39" t="n">
-        <v>91242</v>
+        <v>91872</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4909,10 +4440,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577169</v>
+        <v>577215</v>
       </c>
       <c r="R39" t="n">
-        <v>6711859</v>
+        <v>6711829</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4971,42 +4502,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125687122</v>
+        <v>125687097</v>
       </c>
       <c r="B40" t="n">
-        <v>98352</v>
+        <v>4775</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5015,7 +4542,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577145</v>
+        <v>577154</v>
       </c>
       <c r="R40" t="n">
         <v>6711917</v>
@@ -5077,42 +4604,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125687130</v>
+        <v>125687150</v>
       </c>
       <c r="B41" t="n">
-        <v>98352</v>
+        <v>5179</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5121,10 +4644,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577105</v>
+        <v>577174</v>
       </c>
       <c r="R41" t="n">
-        <v>6711976</v>
+        <v>6711873</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5183,42 +4706,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125687140</v>
+        <v>125687151</v>
       </c>
       <c r="B42" t="n">
-        <v>98352</v>
+        <v>5179</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5227,10 +4746,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577141</v>
+        <v>577176</v>
       </c>
       <c r="R42" t="n">
-        <v>6711960</v>
+        <v>6711840</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5289,10 +4808,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125687151</v>
+        <v>103307641</v>
       </c>
       <c r="B43" t="n">
-        <v>5176</v>
+        <v>99035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5300,42 +4819,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Gstr</t>
+          <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577176</v>
+        <v>577106</v>
       </c>
       <c r="R43" t="n">
-        <v>6711840</v>
+        <v>6711937</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5359,12 +4875,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>I källpåverkat område</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5391,32 +4922,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125687093</v>
+        <v>125687148</v>
       </c>
       <c r="B44" t="n">
-        <v>91242</v>
+        <v>99035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5426,10 +4957,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577243</v>
+        <v>577163</v>
       </c>
       <c r="R44" t="n">
-        <v>6711783</v>
+        <v>6711969</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5488,48 +5019,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125687091</v>
+        <v>57642282</v>
       </c>
       <c r="B45" t="n">
-        <v>91242</v>
+        <v>106813</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>220785</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Gstr</t>
+          <t>Linderåsgruvan 2, Gstr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577156</v>
+        <v>577226</v>
       </c>
       <c r="R45" t="n">
-        <v>6711864</v>
+        <v>6711815</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5553,12 +5084,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5570,63 +5106,64 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
+      <c r="AR45" t="inlineStr"/>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125687090</v>
+        <v>57642283</v>
       </c>
       <c r="B46" t="n">
-        <v>91207</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Gstr</t>
+          <t>Linderåsgruvan 2, Gstr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577215</v>
+        <v>577104</v>
       </c>
       <c r="R46" t="n">
-        <v>6711829</v>
+        <v>6711873</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5650,12 +5187,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5667,25 +5209,26 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
+      <c r="AR46" t="inlineStr"/>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125687145</v>
+        <v>103306833</v>
       </c>
       <c r="B47" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5712,7 +5255,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5720,19 +5263,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Gstr</t>
+          <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>577155</v>
+        <v>577128</v>
       </c>
       <c r="R47" t="n">
-        <v>6711978</v>
+        <v>6711813</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5756,12 +5301,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5788,48 +5343,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125687081</v>
+        <v>103306867</v>
       </c>
       <c r="B48" t="n">
-        <v>96605</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Gstr</t>
+          <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577109</v>
+        <v>577091</v>
       </c>
       <c r="R48" t="n">
-        <v>6711890</v>
+        <v>6711871</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5853,12 +5410,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5885,10 +5452,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125687133</v>
+        <v>103307604</v>
       </c>
       <c r="B49" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5913,29 +5480,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Gstr</t>
+          <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577171</v>
+        <v>577070</v>
       </c>
       <c r="R49" t="n">
-        <v>6711869</v>
+        <v>6711963</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5959,17 +5519,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5996,48 +5561,62 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125687082</v>
+        <v>125512020</v>
       </c>
       <c r="B50" t="n">
-        <v>96605</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Gstr</t>
+          <t>Lars-Lars fäbod, Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577110</v>
+        <v>577196</v>
       </c>
       <c r="R50" t="n">
-        <v>6711911</v>
+        <v>6711856</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6061,12 +5640,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6081,57 +5670,73 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Margareta Kling</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Margareta Kling</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125687152</v>
+        <v>125687110</v>
       </c>
       <c r="B51" t="n">
-        <v>102581</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>223246</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577131</v>
+        <v>577101</v>
       </c>
       <c r="R51" t="n">
-        <v>6711836</v>
+        <v>6711989</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6164,11 +5769,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>12 cm dbh</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6196,10 +5796,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125687131</v>
+        <v>125687111</v>
       </c>
       <c r="B52" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6226,7 +5826,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6240,10 +5840,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577148</v>
+        <v>577182</v>
       </c>
       <c r="R52" t="n">
-        <v>6711976</v>
+        <v>6711920</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6302,45 +5902,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125687149</v>
+        <v>125687112</v>
       </c>
       <c r="B53" t="n">
-        <v>95204</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2383</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>577165</v>
+        <v>577130</v>
       </c>
       <c r="R53" t="n">
-        <v>6711852</v>
+        <v>6711953</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6399,10 +6008,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125687136</v>
+        <v>125687113</v>
       </c>
       <c r="B54" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6429,7 +6038,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6443,10 +6052,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577187</v>
+        <v>577142</v>
       </c>
       <c r="R54" t="n">
-        <v>6711916</v>
+        <v>6711971</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6505,10 +6114,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125687139</v>
+        <v>125687114</v>
       </c>
       <c r="B55" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6535,7 +6144,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6549,10 +6158,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>577090</v>
+        <v>577145</v>
       </c>
       <c r="R55" t="n">
-        <v>6711973</v>
+        <v>6711974</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6611,45 +6220,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125687084</v>
+        <v>125687115</v>
       </c>
       <c r="B56" t="n">
-        <v>96605</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>577088</v>
+        <v>577167</v>
       </c>
       <c r="R56" t="n">
-        <v>6711963</v>
+        <v>6711948</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6708,45 +6326,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125687095</v>
+        <v>125687116</v>
       </c>
       <c r="B57" t="n">
-        <v>91242</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>577135</v>
+        <v>577202</v>
       </c>
       <c r="R57" t="n">
-        <v>6711824</v>
+        <v>6711890</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6805,10 +6432,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125687143</v>
+        <v>125687117</v>
       </c>
       <c r="B58" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6835,7 +6462,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6849,10 +6476,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>577152</v>
+        <v>577124</v>
       </c>
       <c r="R58" t="n">
-        <v>6711960</v>
+        <v>6711978</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6911,45 +6538,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125687085</v>
+        <v>125687118</v>
       </c>
       <c r="B59" t="n">
-        <v>96605</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>577130</v>
+        <v>577129</v>
       </c>
       <c r="R59" t="n">
-        <v>6711985</v>
+        <v>6711973</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7008,10 +6644,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125687114</v>
+        <v>125687119</v>
       </c>
       <c r="B60" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7038,7 +6674,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7052,10 +6688,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577145</v>
+        <v>577190</v>
       </c>
       <c r="R60" t="n">
-        <v>6711974</v>
+        <v>6711913</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7114,10 +6750,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125687141</v>
+        <v>125687120</v>
       </c>
       <c r="B61" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7144,7 +6780,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7152,16 +6788,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>577143</v>
+        <v>577187</v>
       </c>
       <c r="R61" t="n">
-        <v>6711958</v>
+        <v>6711920</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7202,6 +6845,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7220,10 +6864,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125687128</v>
+        <v>125687121</v>
       </c>
       <c r="B62" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7250,7 +6894,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7264,10 +6908,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577194</v>
+        <v>577178</v>
       </c>
       <c r="R62" t="n">
-        <v>6711897</v>
+        <v>6711912</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7326,10 +6970,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125687110</v>
+        <v>125687122</v>
       </c>
       <c r="B63" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7356,7 +7000,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7364,23 +7008,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577101</v>
+        <v>577145</v>
       </c>
       <c r="R63" t="n">
-        <v>6711989</v>
+        <v>6711917</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7421,7 +7058,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7440,10 +7076,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125687113</v>
+        <v>125687123</v>
       </c>
       <c r="B64" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7470,7 +7106,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7484,10 +7120,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>577142</v>
+        <v>577090</v>
       </c>
       <c r="R64" t="n">
-        <v>6711971</v>
+        <v>6711978</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7546,10 +7182,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125687144</v>
+        <v>125687124</v>
       </c>
       <c r="B65" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7576,7 +7212,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7590,10 +7226,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>577150</v>
+        <v>577103</v>
       </c>
       <c r="R65" t="n">
-        <v>6711962</v>
+        <v>6711980</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7652,10 +7288,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125687112</v>
+        <v>125687125</v>
       </c>
       <c r="B66" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7682,7 +7318,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7696,10 +7332,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>577130</v>
+        <v>577172</v>
       </c>
       <c r="R66" t="n">
-        <v>6711953</v>
+        <v>6711942</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7758,10 +7394,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125687134</v>
+        <v>125687126</v>
       </c>
       <c r="B67" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7788,7 +7424,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7802,10 +7438,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>577126</v>
+        <v>577173</v>
       </c>
       <c r="R67" t="n">
-        <v>6711880</v>
+        <v>6711932</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7864,10 +7500,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125687124</v>
+        <v>125687127</v>
       </c>
       <c r="B68" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7894,7 +7530,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7902,16 +7538,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>577103</v>
+        <v>577095</v>
       </c>
       <c r="R68" t="n">
-        <v>6711980</v>
+        <v>6711970</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7952,6 +7595,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7970,10 +7614,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125687137</v>
+        <v>125687128</v>
       </c>
       <c r="B69" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8000,7 +7644,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8014,10 +7658,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>577195</v>
+        <v>577194</v>
       </c>
       <c r="R69" t="n">
-        <v>6711896</v>
+        <v>6711897</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8076,10 +7720,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125687126</v>
+        <v>125687129</v>
       </c>
       <c r="B70" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8106,7 +7750,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8120,10 +7764,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>577173</v>
+        <v>577096</v>
       </c>
       <c r="R70" t="n">
-        <v>6711932</v>
+        <v>6711969</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8182,10 +7826,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125687129</v>
+        <v>125687130</v>
       </c>
       <c r="B71" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8226,10 +7870,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>577096</v>
+        <v>577105</v>
       </c>
       <c r="R71" t="n">
-        <v>6711969</v>
+        <v>6711976</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8288,10 +7932,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125687119</v>
+        <v>125687131</v>
       </c>
       <c r="B72" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8318,7 +7962,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8332,10 +7976,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>577190</v>
+        <v>577148</v>
       </c>
       <c r="R72" t="n">
-        <v>6711913</v>
+        <v>6711976</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8394,10 +8038,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125687115</v>
+        <v>125687132</v>
       </c>
       <c r="B73" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8424,7 +8068,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8438,10 +8082,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>577167</v>
+        <v>577153</v>
       </c>
       <c r="R73" t="n">
-        <v>6711948</v>
+        <v>6711978</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8500,10 +8144,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125687120</v>
+        <v>125687133</v>
       </c>
       <c r="B74" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8530,7 +8174,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8538,23 +8182,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>577187</v>
+        <v>577171</v>
       </c>
       <c r="R74" t="n">
-        <v>6711920</v>
+        <v>6711869</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8589,13 +8226,17 @@
           <t>2025-06-04</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Med gula blad på genom stormfällen uppkommen glänta</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8614,45 +8255,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125687087</v>
+        <v>125687134</v>
       </c>
       <c r="B75" t="n">
-        <v>96605</v>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>577157</v>
+        <v>577126</v>
       </c>
       <c r="R75" t="n">
-        <v>6711975</v>
+        <v>6711880</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8711,45 +8361,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125687148</v>
+        <v>125687135</v>
       </c>
       <c r="B76" t="n">
-        <v>98269</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>577163</v>
+        <v>577117</v>
       </c>
       <c r="R76" t="n">
-        <v>6711969</v>
+        <v>6712004</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8808,10 +8467,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125687125</v>
+        <v>125687136</v>
       </c>
       <c r="B77" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8838,7 +8497,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8852,10 +8511,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>577172</v>
+        <v>577187</v>
       </c>
       <c r="R77" t="n">
-        <v>6711942</v>
+        <v>6711916</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8914,45 +8573,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125687096</v>
+        <v>125687137</v>
       </c>
       <c r="B78" t="n">
-        <v>103794</v>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>577145</v>
+        <v>577195</v>
       </c>
       <c r="R78" t="n">
-        <v>6711831</v>
+        <v>6711896</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9011,45 +8679,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125687088</v>
+        <v>125687139</v>
       </c>
       <c r="B79" t="n">
-        <v>96605</v>
+        <v>99118</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>577173</v>
+        <v>577090</v>
       </c>
       <c r="R79" t="n">
-        <v>6711943</v>
+        <v>6711973</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9108,38 +8785,42 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125687097</v>
+        <v>125687140</v>
       </c>
       <c r="B80" t="n">
-        <v>4772</v>
+        <v>99118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9148,10 +8829,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>577154</v>
+        <v>577141</v>
       </c>
       <c r="R80" t="n">
-        <v>6711917</v>
+        <v>6711960</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9210,10 +8891,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125687146</v>
+        <v>125687141</v>
       </c>
       <c r="B81" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9254,10 +8935,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>577165</v>
+        <v>577143</v>
       </c>
       <c r="R81" t="n">
-        <v>6711956</v>
+        <v>6711958</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9316,45 +8997,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125687094</v>
+        <v>125687142</v>
       </c>
       <c r="B82" t="n">
-        <v>91242</v>
+        <v>99118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lars-Lars fäbod, Gstr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>577189</v>
+        <v>577150</v>
       </c>
       <c r="R82" t="n">
-        <v>6711814</v>
+        <v>6711955</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9413,10 +9103,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125687132</v>
+        <v>125687143</v>
       </c>
       <c r="B83" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9443,7 +9133,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9457,10 +9147,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>577153</v>
+        <v>577152</v>
       </c>
       <c r="R83" t="n">
-        <v>6711978</v>
+        <v>6711960</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9519,10 +9209,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125687117</v>
+        <v>125687144</v>
       </c>
       <c r="B84" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9549,7 +9239,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9563,10 +9253,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>577124</v>
+        <v>577150</v>
       </c>
       <c r="R84" t="n">
-        <v>6711978</v>
+        <v>6711962</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9625,10 +9315,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125687118</v>
+        <v>125687145</v>
       </c>
       <c r="B85" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9655,7 +9345,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -9669,10 +9359,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>577129</v>
+        <v>577155</v>
       </c>
       <c r="R85" t="n">
-        <v>6711973</v>
+        <v>6711978</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9731,10 +9421,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125687135</v>
+        <v>125687146</v>
       </c>
       <c r="B86" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9761,7 +9451,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -9775,10 +9465,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>577117</v>
+        <v>577165</v>
       </c>
       <c r="R86" t="n">
-        <v>6712004</v>
+        <v>6711956</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9840,7 +9530,7 @@
         <v>131983559</v>
       </c>
       <c r="B87" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9934,10 +9624,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131983662</v>
+        <v>57642249</v>
       </c>
       <c r="B88" t="n">
-        <v>96338</v>
+        <v>104628</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9945,37 +9635,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2809</v>
+        <v>222412</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Gstr</t>
+          <t>Linderåsgruvan 1, Gstr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>577133</v>
+        <v>577136</v>
       </c>
       <c r="R88" t="n">
-        <v>6711890</v>
+        <v>6711862</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9999,12 +9689,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10016,63 +9711,64 @@
       <c r="AG88" t="b">
         <v>0</v>
       </c>
+      <c r="AR88" t="inlineStr"/>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131983736</v>
+        <v>57642278</v>
       </c>
       <c r="B89" t="n">
-        <v>97358</v>
+        <v>104628</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>53</v>
+        <v>222412</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lars-Lars fäbod, Gstr</t>
+          <t>Linderåsgruvan 2, Gstr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>577111</v>
+        <v>577171</v>
       </c>
       <c r="R89" t="n">
-        <v>6711904</v>
+        <v>6711820</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10096,12 +9792,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10113,18 +9814,528 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
+      <c r="AR89" t="inlineStr"/>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>57642279</v>
+      </c>
+      <c r="B90" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Linderåsgruvan 2, Gstr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>577215</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6711832</v>
+      </c>
+      <c r="S90" t="n">
+        <v>20</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR90" t="inlineStr"/>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Via Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>57642280</v>
+      </c>
+      <c r="B91" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Linderåsgruvan 2, Gstr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>577142</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6711885</v>
+      </c>
+      <c r="S91" t="n">
+        <v>20</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR91" t="inlineStr"/>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Via Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>125687096</v>
+      </c>
+      <c r="B92" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>577145</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6711831</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>57642281</v>
+      </c>
+      <c r="B93" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Linderåsgruvan 2, Gstr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>577207</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6711897</v>
+      </c>
+      <c r="S93" t="n">
+        <v>20</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR93" t="inlineStr"/>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Via Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>125687152</v>
+      </c>
+      <c r="B94" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Lars-Lars fäbod, Gstr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>577131</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6711836</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>12 cm dbh</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21958-2025 artfynd.xlsx
+++ b/artfynd/A 21958-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AZ94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642289</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642290</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103306856</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103307766</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687078</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687079</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,6 +1422,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687080</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1484,6 +1524,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687081</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687082</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1678,6 +1728,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687083</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1775,6 +1830,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687084</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1872,6 +1932,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687085</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1969,6 +2034,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687086</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2066,6 +2136,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687087</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2163,6 +2238,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687088</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2260,6 +2340,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131983736</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2363,6 +2448,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642307</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2460,6 +2550,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687091</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2557,6 +2652,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687092</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2654,6 +2754,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687093</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2751,6 +2856,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687094</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2848,6 +2958,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687095</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2945,6 +3060,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687149</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3054,6 +3174,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103307676</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3157,6 +3282,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642292</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3260,6 +3390,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642293</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3357,6 +3492,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131983662</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3460,6 +3600,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642294</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3563,6 +3708,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642299</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3674,6 +3824,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1052853</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3777,6 +3932,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642300</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3880,6 +4040,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642302</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3983,6 +4148,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642303</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4086,6 +4256,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642304</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4191,6 +4366,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88898115</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4294,6 +4474,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642305</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4402,6 +4587,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103307852</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4499,6 +4689,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687090</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4601,6 +4796,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687097</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4703,6 +4903,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687150</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4805,6 +5010,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687151</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4919,6 +5129,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103307641</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5016,6 +5231,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687148</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5119,6 +5339,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642282</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5222,6 +5447,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642283</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5340,6 +5570,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103306833</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5449,6 +5684,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103306867</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5558,6 +5798,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103307604</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5679,6 +5924,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125512020</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5793,6 +6043,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687110</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5899,6 +6154,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687111</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6005,6 +6265,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687112</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6111,6 +6376,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687113</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6217,6 +6487,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687114</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6323,6 +6598,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687115</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6429,6 +6709,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687116</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6535,6 +6820,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687117</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6641,6 +6931,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687118</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6747,6 +7042,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687119</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6861,6 +7161,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687120</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6967,6 +7272,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687121</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7073,6 +7383,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687122</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7179,6 +7494,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687123</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7285,6 +7605,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687124</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7391,6 +7716,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687125</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7497,6 +7827,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687126</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7611,6 +7946,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687127</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7717,6 +8057,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687128</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7823,6 +8168,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687129</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7929,6 +8279,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687130</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8035,6 +8390,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687131</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8141,6 +8501,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687132</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8252,6 +8617,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687133</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8358,6 +8728,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687134</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8464,6 +8839,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687135</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8570,6 +8950,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687136</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8676,6 +9061,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687137</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8782,6 +9172,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687139</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8888,6 +9283,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687140</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8994,6 +9394,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687141</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9100,6 +9505,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687142</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9206,6 +9616,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687143</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9312,6 +9727,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687144</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9418,6 +9838,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687145</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9524,6 +9949,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687146</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9621,6 +10051,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131983559</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9724,6 +10159,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642249</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9827,6 +10267,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642278</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9930,6 +10375,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642279</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10033,6 +10483,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642280</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10130,6 +10585,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687096</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10233,6 +10693,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642281</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10336,8 +10801,108 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125687152</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>